--- a/inferences/jesuitas-entrada-full.xlsx
+++ b/inferences/jesuitas-entrada-full.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet_name_1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet_name_1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -496,11 +496,7 @@
           <t>Landeck, Tirol</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q494299"}}</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -533,11 +529,7 @@
           <t>Domfront, diocese de Mans</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -572,7 +564,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[JRC Entrou em Landsberg, Alemanha segundo "http://www.conimbricenses.org/encyclopedia/aigenler-adam/"] extra_info: {"value": {"comment": "Golvers, 2019 @wikidata:Q39793", "original": "?"}}</t>
+          <t>[JRC Entrou em Landsberg, Alemanha segundo "http://www.conimbricenses.org/encyclopedia/aigenler-adam/"]</t>
         </is>
       </c>
     </row>
@@ -673,11 +665,7 @@
           <t>Ilha de S. Miguel, Açores</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412 Ver Brockey, p.230 cit. Carta de A.P. a Viteleschi, de Coimbra, 26 Agosto 1640", "original": "?"}}</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -743,11 +731,7 @@
           <t>Santarém</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -912,11 +896,7 @@
           <t>Nice</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16731105"}, "value": {"comment": "@wikidata:Q490"}}</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -982,11 +962,7 @@
           <t>Sarzana</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1019,11 +995,7 @@
           <t>Murcia, diocese de Cartagena</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1461"}}</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1056,11 +1028,7 @@
           <t>Lyon</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q6397"}}</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1093,11 +1061,7 @@
           <t>Pont-à-Mousson</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16091026 ou 1607"}}</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -1163,11 +1127,7 @@
           <t>Bruxelas</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q494299"}}</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -1200,11 +1160,7 @@
           <t>Orte</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1270,11 +1226,7 @@
           <t>Quintas, diocese de Braga</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1307,11 +1259,7 @@
           <t>Como, Itália</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q9269"}}</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -1344,11 +1292,7 @@
           <t>Macerata</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -1381,11 +1325,7 @@
           <t>Chieti, Abruzzi</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1418,11 +1358,7 @@
           <t>Reggio</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -1455,11 +1391,7 @@
           <t>Bruges</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q162022", "original": "Malines"}}</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -1558,11 +1490,7 @@
           <t>Avignon</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220", "original": "(Noviciado de Sant'Andrea al Quirinale)"}}</t>
-        </is>
-      </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -1661,11 +1589,7 @@
           <t>Mondéjar, Guadalajara</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "? ou 1563?"}, "value": {"comment": "@wikidata:Q46940"}}</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -1698,11 +1622,7 @@
           <t>Pequim</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -1764,11 +1684,7 @@
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "jovem fidalgo"}, "value": {"comment": "@wikidata:Q1171"}}</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -1801,11 +1717,7 @@
           <t>Nisa, diocese de Portalegre</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q179948"}}</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -1900,11 +1812,7 @@
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "entra para a China"}, "value": {"comment": "@wikidata:Q597", "original": "Lisboa, Arroios"}}</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -1937,11 +1845,7 @@
           <t>Porto</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16630325"}, "value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -2007,11 +1911,7 @@
           <t>Campo Maior</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q2478280"}}</t>
-        </is>
-      </c>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -2046,7 +1946,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>[Brockey diz "educated at the College of Coimbra" cap.6 nota 95, citando a carta ânua de 1656, Ajuda, 49-V.14:62v] extra_info: {"value": {"comment": "@wikidata:Q45412 Brockey, cap.6 n.95", "original": "?"}}</t>
+          <t>[Brockey diz "educated at the College of Coimbra" cap.6 nota 95, citando a carta ânua de 1656, Ajuda, 49-V.14:62v]</t>
         </is>
       </c>
     </row>
@@ -2081,11 +1981,7 @@
           <t>Alandroal</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q179948"}}</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -2151,11 +2047,7 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412 Segundo Dominguez &amp; O Neil, V.III,p.2961. Franco Imagem...Coimbra,II,4,c.36,p.575", "original": "?"}}</t>
-        </is>
-      </c>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -2188,11 +2080,7 @@
           <t>Porto</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 17070718"}}</t>
-        </is>
-      </c>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -2225,11 +2113,7 @@
           <t>Porto</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1171"}}</t>
-        </is>
-      </c>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -2262,11 +2146,7 @@
           <t>Mortágua, diocese de Coimbra</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597", "original": "Lisboa, Arroios"}}</t>
-        </is>
-      </c>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -2295,11 +2175,7 @@
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "antes de, nesta data agradece o geral por lhe ter permitido entrar na companhia"}}</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -2332,11 +2208,7 @@
           <t>Lecce</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q2634"}}</t>
-        </is>
-      </c>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -2369,11 +2241,7 @@
           <t>Herzogenburg</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "ou Viena @wikidata:Q131266 ou @wikidata:Q1741"}}</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -2406,11 +2274,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -2443,11 +2307,7 @@
           <t>Lituânia</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q216"}}</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -2480,11 +2340,7 @@
           <t>Macerata</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -2517,11 +2373,7 @@
           <t>Porto</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16931016 ou 16931021 ou 16930326"}, "value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -2554,11 +2406,7 @@
           <t>Moulins</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -2624,11 +2472,7 @@
           <t>Gaillac</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q7880"}}</t>
-        </is>
-      </c>
+      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -2694,11 +2538,7 @@
           <t>Namur</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "inscrito em Namur a 16600908"}, "value": {"comment": "@wikidata:Q173219"}}</t>
-        </is>
-      </c>
+      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -2764,11 +2604,7 @@
           <t>Lourinhã</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q14773"}}</t>
-        </is>
-      </c>
+      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -2801,11 +2637,7 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -2838,11 +2670,7 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16690519"}, "value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -2871,11 +2699,7 @@
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1171", "original": "Goa, \u00cdndia"}}</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -2941,11 +2765,7 @@
           <t>Oleiros, diocese de Portalegre</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "Franco, 1717, p. 375, Sweet, 20216, p.27 @wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -3044,11 +2864,7 @@
           <t>Casal, diocese de Viseu</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16090502 reentroun em 1611 n\u00e3o se sabe onde"}, "value": {"comment": "@wikidata:Q45412 (Franco, 1719, t.II, p. 612)", "original": "?"}}</t>
-        </is>
-      </c>
+      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -3081,11 +2897,7 @@
           <t>Cortiços, diocese de Viseu</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
@@ -3118,11 +2930,7 @@
           <t>Montemor-o-Velho, diocese de Coimbra</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -3188,11 +2996,7 @@
           <t>Portalegre</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -3258,11 +3062,7 @@
           <t>Lavre, diocese de Évora</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "o cat\u00e1logo do Jap\u00e3o de 1697 diz 1675"}}</t>
-        </is>
-      </c>
+      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -3295,11 +3095,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45"}}</t>
-        </is>
-      </c>
+      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -3332,11 +3128,7 @@
           <t>Brescia</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16840127"}, "value": {"comment": "@wikidata:Q1449"}}</t>
-        </is>
-      </c>
+      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -3402,11 +3194,7 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
@@ -3439,11 +3227,7 @@
           <t>Nice</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q490"}}</t>
-        </is>
-      </c>
+      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -3476,11 +3260,7 @@
           <t>Viana do Alentejo, diocese de Évora</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q179948"}}</t>
-        </is>
-      </c>
+      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -3546,11 +3326,7 @@
           <t>Quintela da Lapa</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
@@ -3585,7 +3361,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>attaché d'ambassade extra_info: {"value": {"comment": "@wikidata:Q14773"}}</t>
+          <t>attaché d'ambassade</t>
         </is>
       </c>
     </row>
@@ -3653,11 +3429,7 @@
           <t>Coimbra</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
@@ -3789,11 +3561,7 @@
           <t>Toreguia</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "Goa?"}}</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -3826,11 +3594,7 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "[Arroios Rodrigues, Hist\u00f3ria Da Companhia de Jesus Na Assist\u00eancia de Portugal v4:167] @wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
@@ -3863,11 +3627,7 @@
           <t>Palermo</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "[Sic\u00edlia] @wikidata:Q2656"}}</t>
-        </is>
-      </c>
+      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
@@ -3999,11 +3759,7 @@
           <t>Macau</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "pela segunda vez"}}</t>
-        </is>
-      </c>
+      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -4102,11 +3858,7 @@
           <t>Messina</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "[Sic\u00edlia] @wikidata:Q13666"}}</t>
-        </is>
-      </c>
+      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -4139,11 +3891,7 @@
           <t>San Clemente, diocese de Cuenca</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q471422"}}</t>
-        </is>
-      </c>
+      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
@@ -4275,11 +4023,7 @@
           <t>Arzila, diocese de Coimbra</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q179948"}}</t>
-        </is>
-      </c>
+      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
@@ -4312,11 +4056,7 @@
           <t>Alpedrinha, diocese da Guarda</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45"}}</t>
-        </is>
-      </c>
+      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
@@ -4382,11 +4122,7 @@
           <t>Évora</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1171"}}</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
@@ -4419,11 +4155,7 @@
           <t>Laibach, Carniole</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
-        </is>
-      </c>
+      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
@@ -4456,11 +4188,7 @@
           <t>Lucca</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220", "original": "(Noviciado de Sant'Andrea al Quirinale)"}}</t>
-        </is>
-      </c>
+      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -4559,11 +4287,7 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
@@ -4596,11 +4320,7 @@
           <t>Friuli</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
-        </is>
-      </c>
+      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
@@ -4724,11 +4444,7 @@
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "volta a ser recebido na Companhia"}}</t>
-        </is>
-      </c>
+      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
@@ -4761,11 +4477,7 @@
           <t>Fivizzano</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -4897,11 +4609,7 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1171"}}</t>
-        </is>
-      </c>
+      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
@@ -4967,11 +4675,7 @@
           <t>Coimbra</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
@@ -5004,11 +4708,7 @@
           <t>Porto</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
@@ -5041,11 +4741,7 @@
           <t>Augsburg</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q494299"}}</t>
-        </is>
-      </c>
+      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
@@ -5111,11 +4807,7 @@
           <t>Vila Franca do Campo, ilha de S. Miguel, Açores</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "entra como frade coadjutor"}, "value": {"comment": "suponho que na \u00cdndia"}}</t>
-        </is>
-      </c>
+      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
@@ -5148,11 +4840,7 @@
           <t>Vila Franca do Campo, ilha de S. Miguel, Açores</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "suponho que na \u00cdndia"}}</t>
-        </is>
-      </c>
+      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
@@ -5218,11 +4906,7 @@
           <t>Coimbra</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "[Arroios Rodrigues, Hist\u00f3ria Da Companhia de Jesus Na Assist\u00eancia de Portugal v4:167] @wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
@@ -5321,11 +5005,7 @@
           <t>Longobucco, Calábria</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q2634"}}</t>
-        </is>
-      </c>
+      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
@@ -5391,11 +5071,7 @@
           <t>Emmerich</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q31388", "original": "Tr\u00e8ves"}}</t>
-        </is>
-      </c>
+      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
@@ -5461,11 +5137,7 @@
           <t>Hou-kouang</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "Pequim?"}}</t>
-        </is>
-      </c>
+      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
@@ -5498,11 +5170,7 @@
           <t>Kwangtung</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16950000"}, "value": {"comment": "@wikidata:Q14773"}}</t>
-        </is>
-      </c>
+      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
@@ -5568,11 +5236,7 @@
           <t>Bovalino, Itália</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q2634"}}</t>
-        </is>
-      </c>
+      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
@@ -5605,11 +5269,7 @@
           <t>Fano, Itália</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
@@ -5642,11 +5302,7 @@
           <t>Saluces, Piemonte</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q9269"}}</t>
-        </is>
-      </c>
+      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
@@ -5679,11 +5335,7 @@
           <t>Itália</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "G\u00e9nova?"}}</t>
-        </is>
-      </c>
+      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
@@ -5712,11 +5364,7 @@
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q9269"}}</t>
-        </is>
-      </c>
+      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
@@ -5749,11 +5397,7 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
@@ -5786,11 +5430,7 @@
           <t>Rouen</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "16801225"}, "value": {"comment": "@wikidata:Q1479"}}</t>
-        </is>
-      </c>
+      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
@@ -5856,11 +5496,7 @@
           <t>Genneville, Calvados</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16740907"}, "value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
@@ -5893,11 +5529,7 @@
           <t>Volognes</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
@@ -5963,11 +5595,7 @@
           <t>Peggau</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
-        </is>
-      </c>
+      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
@@ -6099,11 +5727,7 @@
           <t>Cantão</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "venu au service des P\u00e8res? recebido quatro meses antes da sua morte"}}</t>
-        </is>
-      </c>
+      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
@@ -6169,11 +5793,7 @@
           <t>Trébry</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "terceiro de 13 irm\u00e3os"}, "value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
@@ -6206,11 +5826,7 @@
           <t>Bellegarde</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q40898"}}</t>
-        </is>
-      </c>
+      <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
@@ -6243,11 +5859,7 @@
           <t>Verdun</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q40898"}}</t>
-        </is>
-      </c>
+      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
@@ -6280,11 +5892,7 @@
           <t>Compiègne</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q6397"}}</t>
-        </is>
-      </c>
+      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
@@ -6317,11 +5925,7 @@
           <t>Cuneo, Piemonte</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q9269"}}</t>
-        </is>
-      </c>
+      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
@@ -6354,11 +5958,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "f. diz 16720812"}, "value": {"comment": "@wikidata:Q216", "original": "Vilna"}}</t>
-        </is>
-      </c>
+      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
@@ -6391,11 +5991,7 @@
           <t>Valença</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1171"}}</t>
-        </is>
-      </c>
+      <c r="G169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
@@ -6428,11 +6024,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1171"}}</t>
-        </is>
-      </c>
+      <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
@@ -6465,11 +6057,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
@@ -6502,11 +6090,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
@@ -6539,11 +6123,7 @@
           <t>Issoudun</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
@@ -6609,11 +6189,7 @@
           <t>Valdemoro, diocese de Toledo</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "villarejo? @wikidata:Q929997"}}</t>
-        </is>
-      </c>
+      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
@@ -6745,11 +6321,7 @@
           <t>Crato</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q179948"}}</t>
-        </is>
-      </c>
+      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
@@ -6782,11 +6354,7 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
@@ -6819,11 +6387,7 @@
           <t>Mesão Frio, diocese do Porto</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "MMHM:p.219 (Diego de Mesquita)", "original": "?"}}</t>
-        </is>
-      </c>
+      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
@@ -6955,11 +6519,7 @@
           <t>Cerradas, diocese de Lisboa</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 12 Franco, A. (1717). p.916 \"Depois estudou no Collegio de Coimbra\""}, "value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
@@ -7025,11 +6585,7 @@
           <t>Nápoles</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q2634"}}</t>
-        </is>
-      </c>
+      <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
@@ -7062,11 +6618,7 @@
           <t>Lanhoso, diocese de Braga</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
@@ -7132,11 +6684,7 @@
           <t>Vimieiro, diocese de Évora</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q179948"}}</t>
-        </is>
-      </c>
+      <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
@@ -7169,11 +6717,7 @@
           <t>Unhão, diocese de Braga</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
@@ -7305,11 +6849,7 @@
           <t>Hwating (Houa-t'ing), do Song-kiang fou, Kiangsu</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "era um letrado chin\u00eas que se tornou catequista e depois jesu\u00edta"}}</t>
-        </is>
-      </c>
+      <c r="G195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
@@ -7342,11 +6882,7 @@
           <t>Grand-Russey, diocese de Besançon</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q6397"}}</t>
-        </is>
-      </c>
+      <c r="G196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
@@ -7379,11 +6915,7 @@
           <t>Guimarães</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
@@ -7449,11 +6981,7 @@
           <t>Auxerre</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q40898"}}</t>
-        </is>
-      </c>
+      <c r="G199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
@@ -7486,11 +7014,7 @@
           <t>Châlons-en-Champagne</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
@@ -7523,11 +7047,7 @@
           <t>Linz</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q485294"}}</t>
-        </is>
-      </c>
+      <c r="G201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
@@ -7560,11 +7080,7 @@
           <t>Douai</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q173219"}}</t>
-        </is>
-      </c>
+      <c r="G202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
@@ -7630,11 +7146,7 @@
           <t>Rouen</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
@@ -7667,11 +7179,7 @@
           <t>Nanquim</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q956"}}</t>
-        </is>
-      </c>
+      <c r="G205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
@@ -7704,11 +7212,7 @@
           <t>Anobra, diocese de Coimbra</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
@@ -7774,11 +7278,7 @@
           <t>Semide, diocese de Coimbra</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
@@ -7811,11 +7311,7 @@
           <t>Moura, diocese de Évora</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1171"}}</t>
-        </is>
-      </c>
+      <c r="G209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
@@ -7881,11 +7377,7 @@
           <t>Pequim</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q956"}}</t>
-        </is>
-      </c>
+      <c r="G211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
@@ -7918,11 +7410,7 @@
           <t>Mourières, perto d'Avignon</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q6397"}}</t>
-        </is>
-      </c>
+      <c r="G212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
@@ -7955,11 +7443,7 @@
           <t>Rouen</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
@@ -7992,11 +7476,7 @@
           <t>Diocese de Nevers</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
@@ -8029,11 +7509,7 @@
           <t>Pequim</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
@@ -8066,11 +7542,7 @@
           <t>Segno, diocese de Trento</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q494299"}}</t>
-        </is>
-      </c>
+      <c r="G216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
@@ -8103,11 +7575,7 @@
           <t>Guarda</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597", "original": "Lisboa, Arroios"}}</t>
-        </is>
-      </c>
+      <c r="G217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
@@ -8140,11 +7608,7 @@
           <t>Oliveira de Frades, diocese de Viseu</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
@@ -8276,11 +7740,7 @@
           <t>Pitthem, Bélgica</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q162022", "original": "Malines"}}</t>
-        </is>
-      </c>
+      <c r="G222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
@@ -8313,11 +7773,7 @@
           <t>Florença</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220", "original": "(Noviciado de Sant'Andrea al Quirinale)"}}</t>
-        </is>
-      </c>
+      <c r="G223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
@@ -8416,11 +7872,7 @@
           <t>Évora</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 1567"}}</t>
-        </is>
-      </c>
+      <c r="G226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
@@ -8453,11 +7905,7 @@
           <t>Montemor-o-Velho, diocese de Coimbra</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1171"}}</t>
-        </is>
-      </c>
+      <c r="G227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
@@ -8523,11 +7971,7 @@
           <t>Génova</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1449"}}</t>
-        </is>
-      </c>
+      <c r="G229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
@@ -8560,11 +8004,7 @@
           <t>Falkenberg, Silésia</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "[Rep\u00fablica Checa] @wikidata:Q14960"}}</t>
-        </is>
-      </c>
+      <c r="G230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
@@ -8630,11 +8070,7 @@
           <t>Palermo</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q2634"}}</t>
-        </is>
-      </c>
+      <c r="G232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
@@ -8700,11 +8136,7 @@
           <t>Badia di Farfa</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
@@ -8770,11 +8202,7 @@
           <t>Nápoles</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q2634"}}</t>
-        </is>
-      </c>
+      <c r="G236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
@@ -8840,11 +8268,7 @@
           <t>Génova</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1449"}}</t>
-        </is>
-      </c>
+      <c r="G238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
@@ -8910,11 +8334,7 @@
           <t>Bolonha</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
@@ -9112,11 +8532,7 @@
           <t>Lamego</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "se for mesmo ele"}}</t>
-        </is>
-      </c>
+      <c r="G246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
@@ -9215,11 +8631,7 @@
           <t>Ilhas</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
@@ -9285,11 +8697,7 @@
           <t>Macau</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q8686"}}</t>
-        </is>
-      </c>
+      <c r="G251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
@@ -9355,11 +8763,7 @@
           <t>Macau</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "cerca de"}, "value": {"comment": "@wikidata:Q17"}}</t>
-        </is>
-      </c>
+      <c r="G253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
@@ -9392,11 +8796,7 @@
           <t>Macau</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "ILOC"}}</t>
-        </is>
-      </c>
+      <c r="G254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
@@ -9462,11 +8862,7 @@
           <t>Ilha do Faial, Açores</t>
         </is>
       </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412 \"\"\"Franco, Imagem...Coimbra, v.2 p.616; Barbosa Machado, v.3\"\"\"", "original": "?"}}</t>
-        </is>
-      </c>
+      <c r="G256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
@@ -9631,11 +9027,7 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1171"}}</t>
-        </is>
-      </c>
+      <c r="G261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
@@ -9668,11 +9060,7 @@
           <t>Ponte de Lima, diocese de Braga</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="1" t="inlineStr">
@@ -9738,11 +9126,7 @@
           <t>Villanueva de Barcarrota, diocese de Badajoz</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "j\u00e1 \u00e9 padre"}, "value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
@@ -9775,11 +9159,7 @@
           <t>Arganil, diocese de Coimbra</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "Franco, Imagem...Lisboa, 1717, p.577", "original": "?"}}</t>
-        </is>
-      </c>
+      <c r="G265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
@@ -9845,11 +9225,7 @@
           <t>Lousã, diocese de Coimbra</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
@@ -9915,11 +9291,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1171"}}</t>
-        </is>
-      </c>
+      <c r="G269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
@@ -10051,11 +9423,7 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "com 14 anos"}, "value": {"comment": "? @wikidata:Q1171"}}</t>
-        </is>
-      </c>
+      <c r="G273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
@@ -10121,11 +9489,7 @@
           <t>Macau</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q14773"}}</t>
-        </is>
-      </c>
+      <c r="G275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
@@ -10158,11 +9522,7 @@
           <t>Polónia Maior</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q31487"}}</t>
-        </is>
-      </c>
+      <c r="G276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
@@ -10228,11 +9588,7 @@
           <t>Bastia, Córsega</t>
         </is>
       </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q15121"}}</t>
-        </is>
-      </c>
+      <c r="G278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
@@ -10265,11 +9621,7 @@
           <t>Remicourt, Vosges</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q40898"}}</t>
-        </is>
-      </c>
+      <c r="G279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
@@ -10335,11 +9687,7 @@
           <t>Kiangnan</t>
         </is>
       </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 17401120"}}</t>
-        </is>
-      </c>
+      <c r="G281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
@@ -10372,11 +9720,7 @@
           <t>Maastricht</t>
         </is>
       </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q162022", "original": "Malines"}}</t>
-        </is>
-      </c>
+      <c r="G282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
@@ -10409,11 +9753,7 @@
           <t>Hestrud, Hainaut</t>
         </is>
       </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q173219"}}</t>
-        </is>
-      </c>
+      <c r="G283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
@@ -10446,11 +9786,7 @@
           <t>Nanquim</t>
         </is>
       </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "Macau?"}}</t>
-        </is>
-      </c>
+      <c r="G284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
@@ -10516,11 +9852,7 @@
           <t>Diocese de Limoges</t>
         </is>
       </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "La date de son E. est aussi variable, 16 ou 26 sept. 1682., JS 134, 417 dit 16 sept. 1683."}}</t>
-        </is>
-      </c>
+      <c r="G286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
@@ -10553,11 +9885,7 @@
           <t>Hopei</t>
         </is>
       </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "estava no noviciado nessa altura"}, "value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
@@ -10656,11 +9984,7 @@
           <t>Wrocław</t>
         </is>
       </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16840918"}, "value": {"comment": "[Rep\u00fablica Checa] @wikidata:Q14960"}}</t>
-        </is>
-      </c>
+      <c r="G290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
@@ -10726,11 +10050,7 @@
           <t>Wangen</t>
         </is>
       </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
-        </is>
-      </c>
+      <c r="G292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
@@ -10763,11 +10083,7 @@
           <t>Andancette, diocese de Vienne, Dauphiné</t>
         </is>
       </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16800902"}}</t>
-        </is>
-      </c>
+      <c r="G293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
@@ -10833,11 +10149,7 @@
           <t>Pedrógão Grande, perto de Coimbra</t>
         </is>
       </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412 Segundo Louis Buglio 1688", "original": "?"}}</t>
-        </is>
-      </c>
+      <c r="G295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
@@ -10870,11 +10182,7 @@
           <t>Vidigueira, diocese de Évora</t>
         </is>
       </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q179948"}}</t>
-        </is>
-      </c>
+      <c r="G296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
@@ -10907,11 +10215,7 @@
           <t>Viena</t>
         </is>
       </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
-        </is>
-      </c>
+      <c r="G297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
@@ -10940,11 +10244,7 @@
         </is>
       </c>
       <c r="F298" t="inlineStr"/>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
@@ -11010,11 +10310,7 @@
           <t>Siracusa, Sicília</t>
         </is>
       </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
@@ -11047,11 +10343,7 @@
           <t>Porto</t>
         </is>
       </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1171"}}</t>
-        </is>
-      </c>
+      <c r="G301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
@@ -11084,11 +10376,7 @@
           <t>Avis, diocese de Évora</t>
         </is>
       </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q668"}}</t>
-        </is>
-      </c>
+      <c r="G302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
@@ -11121,11 +10409,7 @@
           <t>Corvaceira, diocese de Viseu</t>
         </is>
       </c>
-      <c r="G303" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "MMHM:p.8"}, "value": {"comment": "[Adicionado a partir de Franco, Imagem...Coimbra, II, 522] @wikidata:Q45412", "original": "?"}}</t>
-        </is>
-      </c>
+      <c r="G303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
@@ -11158,11 +10442,7 @@
           <t>Castrofornos, diocese de Viseu</t>
         </is>
       </c>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
@@ -11195,11 +10475,7 @@
           <t>Portel, diocese de Évora</t>
         </is>
       </c>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "segundo Miguel Rodrigues Louren\u00e7o &amp; Ant\u00f3nio Guimar\u00e3es Pinto. (2023).p.31"}}</t>
-        </is>
-      </c>
+      <c r="G305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
@@ -11232,11 +10508,7 @@
           <t>Compton, Somersetshire</t>
         </is>
       </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220", "original": "(Noviciado de Sant'Andrea al Quirinale)"}}</t>
-        </is>
-      </c>
+      <c r="G306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
@@ -11269,11 +10541,7 @@
           <t>Diocese de Bourges</t>
         </is>
       </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
@@ -11339,11 +10607,7 @@
           <t>Bourg-en-Bresse</t>
         </is>
       </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q6397"}}</t>
-        </is>
-      </c>
+      <c r="G309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
@@ -11409,11 +10673,7 @@
           <t>Udine</t>
         </is>
       </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q641"}}</t>
-        </is>
-      </c>
+      <c r="G311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
@@ -11446,11 +10706,7 @@
           <t>Macerata</t>
         </is>
       </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "era j\u00e1 padre"}}</t>
-        </is>
-      </c>
+      <c r="G312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
@@ -11483,11 +10739,7 @@
           <t>Pavia</t>
         </is>
       </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16140507"}, "value": {"comment": "@wikidata:Q22052"}}</t>
-        </is>
-      </c>
+      <c r="G313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
@@ -11586,11 +10838,7 @@
           <t>Nápoles</t>
         </is>
       </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q2634"}}</t>
-        </is>
-      </c>
+      <c r="G316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
@@ -11623,11 +10871,7 @@
           <t>Nice</t>
         </is>
       </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1449"}}</t>
-        </is>
-      </c>
+      <c r="G317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
@@ -11759,11 +11003,7 @@
           <t>«Boius»</t>
         </is>
       </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16991031"}}</t>
-        </is>
-      </c>
+      <c r="G321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
@@ -11796,11 +11036,7 @@
           <t>Saint-Malo</t>
         </is>
       </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "inscreve-se a 8 de Julho"}}</t>
-        </is>
-      </c>
+      <c r="G322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
@@ -11833,11 +11069,7 @@
           <t>Schilpario, Bergamo</t>
         </is>
       </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q100782"}}</t>
-        </is>
-      </c>
+      <c r="G323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
@@ -11870,11 +11102,7 @@
           <t>Strambino, diocese de Ivrea, Piemonte</t>
         </is>
       </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q22052"}}</t>
-        </is>
-      </c>
+      <c r="G324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
@@ -11907,11 +11135,7 @@
           <t>Ferrara</t>
         </is>
       </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "cerca de"}, "value": {"comment": "@wikidata:Q13362"}}</t>
-        </is>
-      </c>
+      <c r="G325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
@@ -12010,11 +11234,7 @@
           <t>Taggia</t>
         </is>
       </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220", "original": "(Noviciado de Sant'Andrea al Quirinale)"}}</t>
-        </is>
-      </c>
+      <c r="G328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
@@ -12080,11 +11300,7 @@
           <t>Ferrara</t>
         </is>
       </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "? @wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
@@ -12117,11 +11333,7 @@
           <t>Maglie, Itália</t>
         </is>
       </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q2634"}}</t>
-        </is>
-      </c>
+      <c r="G331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
@@ -12154,11 +11366,7 @@
           <t>Reggio</t>
         </is>
       </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q2634"}}</t>
-        </is>
-      </c>
+      <c r="G332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
@@ -12191,11 +11399,7 @@
           <t>Montecosaro</t>
         </is>
       </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
@@ -12228,11 +11432,7 @@
           <t>Lucca</t>
         </is>
       </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
@@ -12265,11 +11465,7 @@
           <t>Ponte en Valtellina</t>
         </is>
       </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1449"}}</t>
-        </is>
-      </c>
+      <c r="G335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
@@ -12302,11 +11498,7 @@
           <t>Caltanissetta, Sicília</t>
         </is>
       </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "[Sic\u00edlia] @wikidata:Q2656"}}</t>
-        </is>
-      </c>
+      <c r="G336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
@@ -12339,11 +11531,7 @@
           <t>Bréscia</t>
         </is>
       </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q485294"}}</t>
-        </is>
-      </c>
+      <c r="G337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
@@ -12378,7 +11566,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>"https://roccadellacultura.it/opere-e-contenuti/la-spezieria-dei-gesuiti-di-novellara" extra_info: {"value": {"comment": "@wikidata:Q111218"}}</t>
+          <t>"https://roccadellacultura.it/opere-e-contenuti/la-spezieria-dei-gesuiti-di-novellara"</t>
         </is>
       </c>
     </row>
@@ -12413,11 +11601,7 @@
           <t>Cuneo, Piemonte</t>
         </is>
       </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1449"}}</t>
-        </is>
-      </c>
+      <c r="G339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="1" t="inlineStr">
@@ -12483,11 +11667,7 @@
           <t>Cuneo, Piemonte</t>
         </is>
       </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q9269"}}</t>
-        </is>
-      </c>
+      <c r="G341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="1" t="inlineStr">
@@ -12520,11 +11700,7 @@
           <t>Palermo</t>
         </is>
       </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "[Sic\u00edlia] @wikidata:Q2656"}}</t>
-        </is>
-      </c>
+      <c r="G342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="1" t="inlineStr">
@@ -12557,11 +11733,7 @@
           <t>Milão</t>
         </is>
       </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1449"}}</t>
-        </is>
-      </c>
+      <c r="G343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" s="1" t="inlineStr">
@@ -12594,11 +11766,7 @@
           <t>Florença</t>
         </is>
       </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1449"}}</t>
-        </is>
-      </c>
+      <c r="G344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" s="1" t="inlineStr">
@@ -12631,11 +11799,7 @@
           <t>Vila Viçosa, diocese de Évora</t>
         </is>
       </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="1" t="inlineStr">
@@ -12668,11 +11832,7 @@
           <t>Vila Real, diocese de Braga</t>
         </is>
       </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"original": "? Segundo Sch\u00fctte, p.1174"}}</t>
-        </is>
-      </c>
+      <c r="G346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="1" t="inlineStr">
@@ -12837,11 +11997,7 @@
           <t>Viena</t>
         </is>
       </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
-        </is>
-      </c>
+      <c r="G351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="1" t="inlineStr">
@@ -12940,11 +12096,7 @@
           <t>Tulle</t>
         </is>
       </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1479"}}</t>
-        </is>
-      </c>
+      <c r="G354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="1" t="inlineStr">
@@ -13010,11 +12162,7 @@
           <t>Marthon</t>
         </is>
       </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1479"}}</t>
-        </is>
-      </c>
+      <c r="G356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="1" t="inlineStr">
@@ -13080,11 +12228,7 @@
           <t>Maastricht</t>
         </is>
       </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q162022", "original": "Malines"}}</t>
-        </is>
-      </c>
+      <c r="G358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" s="1" t="inlineStr">
@@ -13117,11 +12261,7 @@
           <t>Nijmegen</t>
         </is>
       </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q162022", "original": "Malines"}}</t>
-        </is>
-      </c>
+      <c r="G359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="1" t="inlineStr">
@@ -13154,11 +12294,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"original": "gallo-belge"}}</t>
-        </is>
-      </c>
+      <c r="G360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="1" t="inlineStr">
@@ -13216,11 +12352,7 @@
           <t>Salzkotten, diocese de Paderborn</t>
         </is>
       </c>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q31388", "original": "Tr\u00e8ves"}}</t>
-        </is>
-      </c>
+      <c r="G362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" s="1" t="inlineStr">
@@ -13253,11 +12385,7 @@
           <t>Navalafuente, diocese de Toledo</t>
         </is>
       </c>
-      <c r="G363" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q46940", "original": "de Henares"}}</t>
-        </is>
-      </c>
+      <c r="G363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" s="1" t="inlineStr">
@@ -13290,11 +12418,7 @@
           <t>Macau</t>
         </is>
       </c>
-      <c r="G364" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "no noviciado"}, "value": {"comment": "@wikidata:Q1346617", "original": "(Chao-tcheou)"}}</t>
-        </is>
-      </c>
+      <c r="G364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="1" t="inlineStr">
@@ -13327,11 +12451,7 @@
           <t>Montdidier</t>
         </is>
       </c>
-      <c r="G365" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "Fran\u00e7a? @wikidata:Q142"}}</t>
-        </is>
-      </c>
+      <c r="G365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" s="1" t="inlineStr">
@@ -13430,11 +12550,7 @@
           <t>Hukwang</t>
         </is>
       </c>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "vice prov\u00edncia de Portugal"}}</t>
-        </is>
-      </c>
+      <c r="G368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="1" t="inlineStr">
@@ -13467,11 +12583,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G369" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "admitido na Companhia depois de torturado pela f\u00e9?"}}</t>
-        </is>
-      </c>
+      <c r="G369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="1" t="inlineStr">
@@ -13537,11 +12649,7 @@
           <t>Sieradz</t>
         </is>
       </c>
-      <c r="G371" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q31487"}}</t>
-        </is>
-      </c>
+      <c r="G371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="1" t="inlineStr">
@@ -13607,11 +12715,7 @@
           <t>Dunkirk</t>
         </is>
       </c>
-      <c r="G373" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q162022", "original": "Malines"}}</t>
-        </is>
-      </c>
+      <c r="G373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="1" t="inlineStr">
@@ -13644,11 +12748,7 @@
           <t>Landsberg-am-Lech, Baviera</t>
         </is>
       </c>
-      <c r="G374" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q494299"}}</t>
-        </is>
-      </c>
+      <c r="G374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" s="1" t="inlineStr">
@@ -13683,7 +12783,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>admitido na companhia extra_info: {"value": {"comment": "@wikidata:Q12995"}}</t>
+          <t>admitido na companhia</t>
         </is>
       </c>
     </row>
@@ -13720,7 +12820,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>entra no noviciado extra_info: {"value": {"comment": "@wikidata:Q162022", "original": "Malines"}}</t>
+          <t>entra no noviciado</t>
         </is>
       </c>
     </row>
@@ -13953,11 +13053,7 @@
           <t>Meãs do Campo, diocese de Coimbra</t>
         </is>
       </c>
-      <c r="G383" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="1" t="inlineStr">
@@ -14023,11 +13119,7 @@
           <t>Norcia, diocese de Spoleto</t>
         </is>
       </c>
-      <c r="G385" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="1" t="inlineStr">
@@ -14122,11 +13214,7 @@
           <t>Hweichow, Houei-tcheou fou, Anhwei, Kiang-nan</t>
         </is>
       </c>
-      <c r="G388" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q956"}}</t>
-        </is>
-      </c>
+      <c r="G388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="1" t="inlineStr">
@@ -14225,11 +13313,7 @@
           <t>Longuyon, diocese de Trier (Meurthe-et-Moselle)</t>
         </is>
       </c>
-      <c r="G391" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q40898"}}</t>
-        </is>
-      </c>
+      <c r="G391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="1" t="inlineStr">
@@ -14262,11 +13346,7 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="G392" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="1" t="inlineStr">
@@ -14299,11 +13379,7 @@
           <t>Compiègne</t>
         </is>
       </c>
-      <c r="G393" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q6397"}}</t>
-        </is>
-      </c>
+      <c r="G393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="1" t="inlineStr">
@@ -14435,11 +13511,7 @@
           <t>Niederberg</t>
         </is>
       </c>
-      <c r="G397" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q31388", "original": "Tr\u00e8ves"}}</t>
-        </is>
-      </c>
+      <c r="G397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="1" t="inlineStr">
@@ -14505,11 +13577,7 @@
           <t>Wikłów</t>
         </is>
       </c>
-      <c r="G399" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
-        </is>
-      </c>
+      <c r="G399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" s="1" t="inlineStr">
@@ -14575,11 +13643,7 @@
           <t>Diocese de Vienne</t>
         </is>
       </c>
-      <c r="G401" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16960918"}}</t>
-        </is>
-      </c>
+      <c r="G401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="1" t="inlineStr">
@@ -14645,11 +13709,7 @@
           <t>Diocese de Saint-Flour</t>
         </is>
       </c>
-      <c r="G403" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q7880"}}</t>
-        </is>
-      </c>
+      <c r="G403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="1" t="inlineStr">
@@ -14748,11 +13808,7 @@
           <t>Arras</t>
         </is>
       </c>
-      <c r="G406" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" s="1" t="inlineStr">
@@ -14818,11 +13874,7 @@
           <t>Pequim</t>
         </is>
       </c>
-      <c r="G408" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "morre no pr\u00f3prio dia"}, "value": {"comment": "@wikidata:Q956"}}</t>
-        </is>
-      </c>
+      <c r="G408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" s="1" t="inlineStr">
@@ -14855,11 +13907,7 @@
           <t>Boucagnères (palácio do marquês de Grammont), Gasconha</t>
         </is>
       </c>
-      <c r="G409" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q7880"}}</t>
-        </is>
-      </c>
+      <c r="G409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="1" t="inlineStr">
@@ -14892,11 +13940,7 @@
           <t>Mons</t>
         </is>
       </c>
-      <c r="G410" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q173219"}}</t>
-        </is>
-      </c>
+      <c r="G410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" s="1" t="inlineStr">
@@ -14929,11 +13973,7 @@
           <t>Istres</t>
         </is>
       </c>
-      <c r="G411" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q6397"}}</t>
-        </is>
-      </c>
+      <c r="G411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="1" t="inlineStr">
@@ -14966,11 +14006,7 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="G412" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" s="1" t="inlineStr">
@@ -15003,11 +14039,7 @@
           <t>Colmar</t>
         </is>
       </c>
-      <c r="G413" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" s="1" t="inlineStr">
@@ -15172,11 +14204,7 @@
           <t>Diocese de S. Pol de Léon, Bretanha</t>
         </is>
       </c>
-      <c r="G418" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" s="1" t="inlineStr">
@@ -15209,11 +14237,7 @@
           <t>Ath, Hainaut</t>
         </is>
       </c>
-      <c r="G419" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q173219"}}</t>
-        </is>
-      </c>
+      <c r="G419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" s="1" t="inlineStr">
@@ -15246,11 +14270,7 @@
           <t>Diocese de Lyon</t>
         </is>
       </c>
-      <c r="G420" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "Lyon? @wikidata:Q456"}}</t>
-        </is>
-      </c>
+      <c r="G420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="1" t="inlineStr">
@@ -15283,11 +14303,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="G421" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q14773"}}</t>
-        </is>
-      </c>
+      <c r="G421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" s="1" t="inlineStr">
@@ -15320,11 +14336,7 @@
           <t>Lille</t>
         </is>
       </c>
-      <c r="G422" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q193826"}}</t>
-        </is>
-      </c>
+      <c r="G422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="1" t="inlineStr">
@@ -15357,11 +14369,7 @@
           <t>Dole, Jura</t>
         </is>
       </c>
-      <c r="G423" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q6397"}}</t>
-        </is>
-      </c>
+      <c r="G423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" s="1" t="inlineStr">
@@ -15427,11 +14435,7 @@
           <t>Süanhwa (Siuan-houa) fou</t>
         </is>
       </c>
-      <c r="G425" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"original": "dans la mission"}}</t>
-        </is>
-      </c>
+      <c r="G425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" s="1" t="inlineStr">
@@ -15464,11 +14468,7 @@
           <t>Sunwui (Sin-houei hien), Kwangtung</t>
         </is>
       </c>
-      <c r="G426" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q16666"}}</t>
-        </is>
-      </c>
+      <c r="G426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" s="1" t="inlineStr">
@@ -15501,11 +14501,7 @@
           <t>Diocese de Reims</t>
         </is>
       </c>
-      <c r="G427" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q40898"}}</t>
-        </is>
-      </c>
+      <c r="G427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" s="1" t="inlineStr">
@@ -15571,11 +14567,7 @@
           <t>Strasbourg</t>
         </is>
       </c>
-      <c r="G429" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q40898"}}</t>
-        </is>
-      </c>
+      <c r="G429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" s="1" t="inlineStr">
@@ -15608,11 +14600,7 @@
           <t>Maché</t>
         </is>
       </c>
-      <c r="G430" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q6397"}}</t>
-        </is>
-      </c>
+      <c r="G430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" s="1" t="inlineStr">
@@ -15645,11 +14633,7 @@
           <t>Vézelay, diocese de Autun</t>
         </is>
       </c>
-      <c r="G431" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" s="1" t="inlineStr">
@@ -15682,11 +14666,7 @@
           <t>Verdun</t>
         </is>
       </c>
-      <c r="G432" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q40898"}}</t>
-        </is>
-      </c>
+      <c r="G432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" s="1" t="inlineStr">
@@ -15785,11 +14765,7 @@
           <t>Cantão</t>
         </is>
       </c>
-      <c r="G435" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 17321231"}}</t>
-        </is>
-      </c>
+      <c r="G435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="1" t="inlineStr">
@@ -15822,11 +14798,7 @@
           <t>Auvergne</t>
         </is>
       </c>
-      <c r="G436" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q7880"}}</t>
-        </is>
-      </c>
+      <c r="G436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" s="1" t="inlineStr">
@@ -15859,11 +14831,7 @@
           <t>Toulon</t>
         </is>
       </c>
-      <c r="G437" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q6397"}}</t>
-        </is>
-      </c>
+      <c r="G437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" s="1" t="inlineStr">
@@ -15962,11 +14930,7 @@
           <t>Thionville</t>
         </is>
       </c>
-      <c r="G440" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q40898"}}</t>
-        </is>
-      </c>
+      <c r="G440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" s="1" t="inlineStr">
@@ -15999,11 +14963,7 @@
           <t>Pequim</t>
         </is>
       </c>
-      <c r="G441" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q956"}}</t>
-        </is>
-      </c>
+      <c r="G441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" s="1" t="inlineStr">
@@ -16102,11 +15062,7 @@
           <t>Süanhwa, Hopei</t>
         </is>
       </c>
-      <c r="G444" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" s="1" t="inlineStr">
@@ -16172,11 +15128,7 @@
           <t>Lescar, Béarn (paróquia de St. Julien de Lescar)</t>
         </is>
       </c>
-      <c r="G446" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16800422"}}</t>
-        </is>
-      </c>
+      <c r="G446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" s="1" t="inlineStr">
@@ -16209,11 +15161,7 @@
           <t>Kiang-si</t>
         </is>
       </c>
-      <c r="G447" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q14773"}}</t>
-        </is>
-      </c>
+      <c r="G447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" s="1" t="inlineStr">
@@ -16345,11 +15293,7 @@
           <t>Ninove</t>
         </is>
       </c>
-      <c r="G451" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q162022", "original": "Malines"}}</t>
-        </is>
-      </c>
+      <c r="G451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" s="1" t="inlineStr">
@@ -16382,11 +15326,7 @@
           <t>Hweichow (Houei-tcheou fou) (bairro de Ché-hien), Anhwei (Ngan-houei)</t>
         </is>
       </c>
-      <c r="G452" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q956"}}</t>
-        </is>
-      </c>
+      <c r="G452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" s="1" t="inlineStr">
@@ -16551,11 +15491,7 @@
           <t>Hamburgo</t>
         </is>
       </c>
-      <c r="G457" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45"}}</t>
-        </is>
-      </c>
+      <c r="G457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" s="1" t="inlineStr">
@@ -16654,11 +15590,7 @@
           <t>Bombarral, diocese de Lisboa</t>
         </is>
       </c>
-      <c r="G460" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "alternativa"}}</t>
-        </is>
-      </c>
+      <c r="G460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" s="1" t="inlineStr">
@@ -16790,11 +15722,7 @@
           <t>Azeitão, diocese de Lisboa</t>
         </is>
       </c>
-      <c r="G464" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "MMHM, p.91", "original": "?"}}</t>
-        </is>
-      </c>
+      <c r="G464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" s="1" t="inlineStr">
@@ -16827,11 +15755,7 @@
           <t>Coimbra</t>
         </is>
       </c>
-      <c r="G465" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" s="1" t="inlineStr">
@@ -16932,7 +15856,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>Corrigido: local de entrada extra_info: {"value": {"comment": "@wikidata:Q45412 Em Coimbra no ano de 1582 segundo a Carta Annua de 1623 BA", "original": "?"}}</t>
+          <t>Corrigido: local de entrada</t>
         </is>
       </c>
     </row>
@@ -16967,11 +15891,7 @@
           <t>São João de Areias</t>
         </is>
       </c>
-      <c r="G469" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" s="1" t="inlineStr">
@@ -17202,11 +16122,7 @@
           <t>Sabugal, diocese de Lamego</t>
         </is>
       </c>
-      <c r="G476" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" s="1" t="inlineStr">
@@ -17239,11 +16155,7 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G477" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 1729"}}</t>
-        </is>
-      </c>
+      <c r="G477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" s="1" t="inlineStr">
@@ -17276,11 +16188,7 @@
           <t>Portalegre</t>
         </is>
       </c>
-      <c r="G478" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q179948"}}</t>
-        </is>
-      </c>
+      <c r="G478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" s="1" t="inlineStr">
@@ -17346,11 +16254,7 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G480" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 1689"}}</t>
-        </is>
-      </c>
+      <c r="G480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" s="1" t="inlineStr">
@@ -17482,11 +16386,7 @@
           <t>Portalegre</t>
         </is>
       </c>
-      <c r="G484" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "MMHM:p.155, com 19 anos", "original": "?"}}</t>
-        </is>
-      </c>
+      <c r="G484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" s="1" t="inlineStr">
@@ -17552,11 +16452,7 @@
           <t>Coimbra</t>
         </is>
       </c>
-      <c r="G486" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" s="1" t="inlineStr">
@@ -17589,11 +16485,7 @@
           <t>Chaves</t>
         </is>
       </c>
-      <c r="G487" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" s="1" t="inlineStr">
@@ -17659,11 +16551,7 @@
           <t>Macau</t>
         </is>
       </c>
-      <c r="G489" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 19 ou 28"}}</t>
-        </is>
-      </c>
+      <c r="G489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" s="1" t="inlineStr">
@@ -17729,11 +16617,7 @@
           <t>Redondo, diocese de Évora</t>
         </is>
       </c>
-      <c r="G491" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q179948"}}</t>
-        </is>
-      </c>
+      <c r="G491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" s="1" t="inlineStr">
@@ -17766,11 +16650,7 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G492" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "cerca de, estava no noviciado nesta data"}, "value": {"comment": "@wikidata:Q1171"}}</t>
-        </is>
-      </c>
+      <c r="G492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" s="1" t="inlineStr">
@@ -17803,11 +16683,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G493" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" s="1" t="inlineStr">
@@ -17840,11 +16716,7 @@
           <t>Alcochete, diocese de Lisboa</t>
         </is>
       </c>
-      <c r="G494" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" s="1" t="inlineStr">
@@ -17877,11 +16749,7 @@
           <t>Sernancelhe, diocese de Lamego</t>
         </is>
       </c>
-      <c r="G495" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q17"}}</t>
-        </is>
-      </c>
+      <c r="G495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" s="1" t="inlineStr">
@@ -17947,11 +16815,7 @@
           <t>Montemor-o-Velho, diocese de Coimbra</t>
         </is>
       </c>
-      <c r="G497" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" s="1" t="inlineStr">
@@ -18017,11 +16881,7 @@
           <t>Cadaval, diocese de Coimbra</t>
         </is>
       </c>
-      <c r="G499" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" s="1" t="inlineStr">
@@ -18054,11 +16914,7 @@
           <t>Colónia</t>
         </is>
       </c>
-      <c r="G500" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220", "original": "(Noviciado de Sant'Andrea al Quirinale)"}}</t>
-        </is>
-      </c>
+      <c r="G500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" s="1" t="inlineStr">
@@ -18124,11 +16980,7 @@
           <t>Fulda</t>
         </is>
       </c>
-      <c r="G502" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" s="1" t="inlineStr">
@@ -18161,11 +17013,7 @@
           <t>Gorizia</t>
         </is>
       </c>
-      <c r="G503" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "j\u00e1 padre"}, "value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
-        </is>
-      </c>
+      <c r="G503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" s="1" t="inlineStr">
@@ -18198,11 +17046,7 @@
           <t>Sankt Florian</t>
         </is>
       </c>
-      <c r="G504" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
-        </is>
-      </c>
+      <c r="G504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" s="1" t="inlineStr">
@@ -18268,11 +17112,7 @@
           <t>Praga</t>
         </is>
       </c>
-      <c r="G506" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "[Rep\u00fablica Checa] @wikidata:Q14960"}}</t>
-        </is>
-      </c>
+      <c r="G506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" s="1" t="inlineStr">
@@ -18338,11 +17178,7 @@
           <t>Polotsk</t>
         </is>
       </c>
-      <c r="G508" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "hoje Bielorr\u00fassia @wikidata:Q200797"}}</t>
-        </is>
-      </c>
+      <c r="G508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" s="1" t="inlineStr">
@@ -18375,11 +17211,7 @@
           <t>Diocese de Constance (parte da Suábia) no grão-ducado de Bade</t>
         </is>
       </c>
-      <c r="G509" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" s="1" t="inlineStr">
@@ -18412,11 +17244,7 @@
           <t>Split, Croácia</t>
         </is>
       </c>
-      <c r="G510" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" s="1" t="inlineStr">
@@ -18449,11 +17277,7 @@
           <t>Žilina, Eslováquia</t>
         </is>
       </c>
-      <c r="G511" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 17291009"}, "value": {"comment": "@wikidata:Q39193"}}</t>
-        </is>
-      </c>
+      <c r="G511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" s="1" t="inlineStr">
@@ -18519,11 +17343,7 @@
           <t>Cracóvia</t>
         </is>
       </c>
-      <c r="G513" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q31487"}}</t>
-        </is>
-      </c>
+      <c r="G513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" s="1" t="inlineStr">
@@ -18556,11 +17376,7 @@
           <t>Penela, diocese de Coimbra</t>
         </is>
       </c>
-      <c r="G514" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q15041623", "original": "Lisboa, Arroios"}}</t>
-        </is>
-      </c>
+      <c r="G514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" s="1" t="inlineStr">
@@ -18696,11 +17512,7 @@
           <t>Arcos, diocese de Coimbra</t>
         </is>
       </c>
-      <c r="G518" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "cerca de"}}</t>
-        </is>
-      </c>
+      <c r="G518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" s="1" t="inlineStr">
@@ -18898,11 +17710,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G524" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "segundo Pf."}}</t>
-        </is>
-      </c>
+      <c r="G524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" s="1" t="inlineStr">
@@ -18935,11 +17743,7 @@
           <t>Coimbra</t>
         </is>
       </c>
-      <c r="G525" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" s="1" t="inlineStr">
@@ -18972,11 +17776,7 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G526" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 1663"}}</t>
-        </is>
-      </c>
+      <c r="G526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" s="1" t="inlineStr">
@@ -19009,11 +17809,7 @@
           <t>Porto</t>
         </is>
       </c>
-      <c r="G527" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" s="1" t="inlineStr">
@@ -19046,11 +17842,7 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G528" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" s="1" t="inlineStr">
@@ -19083,11 +17875,7 @@
           <t>Benasque, Huesca</t>
         </is>
       </c>
-      <c r="G529" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q31926034"}}</t>
-        </is>
-      </c>
+      <c r="G529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" s="1" t="inlineStr">
@@ -19186,11 +17974,7 @@
           <t>Santa Comba Dão, diocese de Coimbra</t>
         </is>
       </c>
-      <c r="G532" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "a 15, 23 ou 25"}}</t>
-        </is>
-      </c>
+      <c r="G532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" s="1" t="inlineStr">
@@ -19223,11 +18007,7 @@
           <t>Burghausen</t>
         </is>
       </c>
-      <c r="G533" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q494299"}}</t>
-        </is>
-      </c>
+      <c r="G533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" s="1" t="inlineStr">
@@ -19260,11 +18040,7 @@
           <t>Frankenstein, Silésia</t>
         </is>
       </c>
-      <c r="G534" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "actual Eslov\u00e1quia @wikidata:Q145002"}}</t>
-        </is>
-      </c>
+      <c r="G534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" s="1" t="inlineStr">
@@ -19297,11 +18073,7 @@
           <t>Munique</t>
         </is>
       </c>
-      <c r="G535" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q494299"}}</t>
-        </is>
-      </c>
+      <c r="G535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" s="1" t="inlineStr">
@@ -19334,11 +18106,7 @@
           <t>Bolzano, diocese de Trento</t>
         </is>
       </c>
-      <c r="G536" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q494299"}}</t>
-        </is>
-      </c>
+      <c r="G536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" s="1" t="inlineStr">
@@ -19404,11 +18172,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G538" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "novi\u00e7o"}}</t>
-        </is>
-      </c>
+      <c r="G538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" s="1" t="inlineStr">
@@ -19573,11 +18337,7 @@
           <t>Tournai</t>
         </is>
       </c>
-      <c r="G543" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q173219"}}</t>
-        </is>
-      </c>
+      <c r="G543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" s="1" t="inlineStr">
@@ -19610,11 +18370,7 @@
           <t>Montmédy</t>
         </is>
       </c>
-      <c r="G544" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q40898"}}</t>
-        </is>
-      </c>
+      <c r="G544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" s="1" t="inlineStr">
@@ -19647,11 +18403,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="G545" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "vice-prov\u00edncia @wikidata:Q148"}}</t>
-        </is>
-      </c>
+      <c r="G545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" s="1" t="inlineStr">
@@ -19717,11 +18469,7 @@
           <t>Blois</t>
         </is>
       </c>
-      <c r="G547" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" s="1" t="inlineStr">
@@ -19754,11 +18502,7 @@
           <t>Sou-kiang fou, Kiangnan</t>
         </is>
       </c>
-      <c r="G548" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q956"}}</t>
-        </is>
-      </c>
+      <c r="G548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" s="1" t="inlineStr">
@@ -19824,11 +18568,7 @@
           <t>Tarazona</t>
         </is>
       </c>
-      <c r="G550" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q31926034"}}</t>
-        </is>
-      </c>
+      <c r="G550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" s="1" t="inlineStr">
@@ -19927,11 +18667,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="G553" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "diz que esteve em miss\u00e3o num semestre em 1681, n\u00e3o est\u00e1 no cat\u00e1logo de 1683"}}</t>
-        </is>
-      </c>
+      <c r="G553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" s="1" t="inlineStr">
@@ -19964,11 +18700,7 @@
           <t>Saint-Malo</t>
         </is>
       </c>
-      <c r="G554" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" s="1" t="inlineStr">
@@ -20001,11 +18733,7 @@
           <t>Kiangsi</t>
         </is>
       </c>
-      <c r="G555" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q4970"}}</t>
-        </is>
-      </c>
+      <c r="G555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" s="1" t="inlineStr">
@@ -20038,11 +18766,7 @@
           <t>Josselin, Bretanha</t>
         </is>
       </c>
-      <c r="G556" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" s="1" t="inlineStr">
@@ -20108,11 +18832,7 @@
           <t>Boémia</t>
         </is>
       </c>
-      <c r="G558" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "cerca de"}, "value": {"comment": "@wikidata:Q1171"}}</t>
-        </is>
-      </c>
+      <c r="G558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" s="1" t="inlineStr">
@@ -20145,11 +18865,7 @@
           <t>Jimramov, República Checa</t>
         </is>
       </c>
-      <c r="G559" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "[Rep\u00fablica Checa] @wikidata:Q14960"}}</t>
-        </is>
-      </c>
+      <c r="G559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" s="1" t="inlineStr">
@@ -20182,11 +18898,7 @@
           <t>Munique</t>
         </is>
       </c>
-      <c r="G560" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q494299"}}</t>
-        </is>
-      </c>
+      <c r="G560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" s="1" t="inlineStr">
@@ -20219,11 +18931,7 @@
           <t>Würzburg, Baviera</t>
         </is>
       </c>
-      <c r="G561" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1720", "original": "Mayence"}}</t>
-        </is>
-      </c>
+      <c r="G561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" s="1" t="inlineStr">
@@ -20258,7 +18966,7 @@
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>destinado à China em 1785, viagem abortada extra_info: {"value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
+          <t>destinado à China em 1785, viagem abortada</t>
         </is>
       </c>
     </row>
@@ -20293,11 +19001,7 @@
           <t>Sarzana</t>
         </is>
       </c>
-      <c r="G563" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220", "original": "(Noviciado de Sant'Andrea al Quirinale)"}}</t>
-        </is>
-      </c>
+      <c r="G563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" s="1" t="inlineStr">
@@ -20330,11 +19034,7 @@
           <t>Sevilha</t>
         </is>
       </c>
-      <c r="G564" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q2868"}}</t>
-        </is>
-      </c>
+      <c r="G564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" s="1" t="inlineStr">
@@ -20433,11 +19133,7 @@
           <t>Chaves</t>
         </is>
       </c>
-      <c r="G567" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" s="1" t="inlineStr">
@@ -20538,7 +19234,7 @@
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>antes entrara na ordem de Malta em 16120518 diz Dehergne «La première entrée — avant « l'âge de raison » — est une « E. de dévotion », désirée par ses parents, qui consacrent leur fils au Seigneur et le revêtent des habits de l'Ordre, les Chevaliers de Malte.» extra_info: {"value": {"comment": "[Sic\u00edlia] @wikidata:Q2656"}}</t>
+          <t>antes entrara na ordem de Malta em 16120518 diz Dehergne «La première entrée — avant « l'âge de raison » — est une « E. de dévotion », désirée par ses parents, qui consacrent leur fils au Seigneur et le revêtent des habits de l'Ordre, les Chevaliers de Malte.»</t>
         </is>
       </c>
     </row>
@@ -20573,11 +19269,7 @@
           <t>Lorraine</t>
         </is>
       </c>
-      <c r="G571" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" s="1" t="inlineStr">
@@ -20610,11 +19302,7 @@
           <t>Touraine</t>
         </is>
       </c>
-      <c r="G572" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" s="1" t="inlineStr">
@@ -20647,11 +19335,7 @@
           <t>Loches (Indre-et-Loire)</t>
         </is>
       </c>
-      <c r="G573" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16661211"}}</t>
-        </is>
-      </c>
+      <c r="G573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" s="1" t="inlineStr">
@@ -20684,11 +19368,7 @@
           <t>região d'Avranches</t>
         </is>
       </c>
-      <c r="G574" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" s="1" t="inlineStr">
@@ -20721,11 +19401,7 @@
           <t>Bordeaux</t>
         </is>
       </c>
-      <c r="G575" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1479"}}</t>
-        </is>
-      </c>
+      <c r="G575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" s="1" t="inlineStr">
@@ -20791,11 +19467,7 @@
           <t>Kiangchow, Shansi</t>
         </is>
       </c>
-      <c r="G577" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" s="1" t="inlineStr">
@@ -20894,11 +19566,7 @@
           <t>Clisson</t>
         </is>
       </c>
-      <c r="G580" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 17221128"}}</t>
-        </is>
-      </c>
+      <c r="G580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" s="1" t="inlineStr">
@@ -20931,11 +19599,7 @@
           <t>Lyon</t>
         </is>
       </c>
-      <c r="G581" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q6397"}}</t>
-        </is>
-      </c>
+      <c r="G581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" s="1" t="inlineStr">
@@ -20968,11 +19632,7 @@
           <t>Calais</t>
         </is>
       </c>
-      <c r="G582" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G582" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" s="1" t="inlineStr">
@@ -21038,11 +19698,7 @@
           <t>Tours</t>
         </is>
       </c>
-      <c r="G584" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" s="1" t="inlineStr">
@@ -21108,11 +19764,7 @@
           <t>Évora</t>
         </is>
       </c>
-      <c r="G586" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 15600325 ou Coimbra, 25-03-1560 MMHM"}, "value": {"comment": "@wikidata:Q45412 Domingues &amp; O Neil, IV: 2645. MMHM:p.226", "original": "?"}}</t>
-        </is>
-      </c>
+      <c r="G586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" s="1" t="inlineStr">
@@ -21211,11 +19863,7 @@
           <t>Génova, Itália</t>
         </is>
       </c>
-      <c r="G589" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1449"}}</t>
-        </is>
-      </c>
+      <c r="G589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" s="1" t="inlineStr">
@@ -21281,11 +19929,7 @@
           <t>Mântua</t>
         </is>
       </c>
-      <c r="G591" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1891"}}</t>
-        </is>
-      </c>
+      <c r="G591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" s="1" t="inlineStr">
@@ -21318,11 +19962,7 @@
           <t>Alvito, diocese de Évora</t>
         </is>
       </c>
-      <c r="G592" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q179948"}}</t>
-        </is>
-      </c>
+      <c r="G592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" s="1" t="inlineStr">
@@ -21388,11 +20028,7 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G594" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "como \"indiferente\" ou auxiliar laico"}, "value": {"comment": "@wikidata:Q17"}}</t>
-        </is>
-      </c>
+      <c r="G594" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" s="1" t="inlineStr">
@@ -21425,11 +20061,7 @@
           <t>Valadares, diocese de Braga</t>
         </is>
       </c>
-      <c r="G595" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 17051224"}, "value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G595" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" s="1" t="inlineStr">
@@ -21565,11 +20197,7 @@
           <t>Macau</t>
         </is>
       </c>
-      <c r="G599" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16460000"}}</t>
-        </is>
-      </c>
+      <c r="G599" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" s="1" t="inlineStr">
@@ -21602,11 +20230,7 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G600" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G600" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" s="1" t="inlineStr">
@@ -21635,11 +20259,7 @@
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G601" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1171"}}</t>
-        </is>
-      </c>
+      <c r="G601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" s="1" t="inlineStr">
@@ -21668,11 +20288,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G602" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1171"}}</t>
-        </is>
-      </c>
+      <c r="G602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" s="1" t="inlineStr">
@@ -21804,11 +20420,7 @@
           <t>Macau</t>
         </is>
       </c>
-      <c r="G606" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q4970"}}</t>
-        </is>
-      </c>
+      <c r="G606" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" s="1" t="inlineStr">
@@ -21940,11 +20552,7 @@
           <t>Macau</t>
         </is>
       </c>
-      <c r="G610" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 31"}, "value": {"comment": "@wikidata:Q1171"}}</t>
-        </is>
-      </c>
+      <c r="G610" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" s="1" t="inlineStr">
@@ -22043,11 +20651,7 @@
           <t>Polónia</t>
         </is>
       </c>
-      <c r="G613" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q643843", "original": "province de Masovie"}}</t>
-        </is>
-      </c>
+      <c r="G613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" s="1" t="inlineStr">
@@ -22113,11 +20717,7 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G615" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16811103 ou 16811112 ou 16820000"}, "value": {"comment": "@wikidata:Q1171"}}</t>
-        </is>
-      </c>
+      <c r="G615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" s="1" t="inlineStr">
@@ -22183,11 +20783,7 @@
           <t>Tancos, diocese de Lisboa</t>
         </is>
       </c>
-      <c r="G617" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "se for ele"}}</t>
-        </is>
-      </c>
+      <c r="G617" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" s="1" t="inlineStr">
@@ -22253,11 +20849,7 @@
           <t>Figueiró, diocese de Coimbra</t>
         </is>
       </c>
-      <c r="G619" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "estava j\u00e1 no noviciado"}}</t>
-        </is>
-      </c>
+      <c r="G619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" s="1" t="inlineStr">
@@ -22290,11 +20882,7 @@
           <t>Figueiró-do-Campo, diocese de Coimbra</t>
         </is>
       </c>
-      <c r="G620" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 17481215"}, "value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G620" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" s="1" t="inlineStr">
@@ -22393,11 +20981,7 @@
           <t>Setúbal</t>
         </is>
       </c>
-      <c r="G623" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q179948"}}</t>
-        </is>
-      </c>
+      <c r="G623" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" s="1" t="inlineStr">
@@ -22531,7 +21115,7 @@
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>talvez tenha saído durante o noviciado extra_info: {"value": {"comment": "para a China"}}</t>
+          <t>talvez tenha saído durante o noviciado</t>
         </is>
       </c>
     </row>
@@ -22599,11 +21183,7 @@
           <t>Viseu</t>
         </is>
       </c>
-      <c r="G629" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q179948"}}</t>
-        </is>
-      </c>
+      <c r="G629" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" s="1" t="inlineStr">
@@ -22702,11 +21282,7 @@
           <t>Torre de Moncorvo, diocese de Braga</t>
         </is>
       </c>
-      <c r="G632" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" s="1" t="inlineStr">
@@ -22774,7 +21350,7 @@
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>segundo a entrada de Rhodes (677), este baptizou-o extra_info: {"date": {"comment": "vem com o P. Alexandre de Rhodes"}, "value": {"comment": "@wikidata:Q220"}}</t>
+          <t>segundo a entrada de Rhodes (677), este baptizou-o</t>
         </is>
       </c>
     </row>
@@ -22842,11 +21418,7 @@
           <t>Castelo Branco</t>
         </is>
       </c>
-      <c r="G636" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412 Segungo Dominguez, J. M., &amp; O\u2019Neill, C. (2001) II, 1113", "original": "?"}}</t>
-        </is>
-      </c>
+      <c r="G636" t="inlineStr"/>
     </row>
     <row r="637">
       <c r="A637" s="1" t="inlineStr">
@@ -22879,11 +21451,7 @@
           <t>Alpalhão, diocese de Portalegre</t>
         </is>
       </c>
-      <c r="G637" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q179948"}}</t>
-        </is>
-      </c>
+      <c r="G637" t="inlineStr"/>
     </row>
     <row r="638">
       <c r="A638" s="1" t="inlineStr">
@@ -22949,11 +21517,7 @@
           <t>São João Batista de Lobrigos, diocese do Porto</t>
         </is>
       </c>
-      <c r="G639" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412 Schutte, Monumenta historica japoniae I.,p.1180", "original": "?"}}</t>
-        </is>
-      </c>
+      <c r="G639" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" s="1" t="inlineStr">
@@ -23019,11 +21583,7 @@
           <t>Macau</t>
         </is>
       </c>
-      <c r="G641" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q14773"}}</t>
-        </is>
-      </c>
+      <c r="G641" t="inlineStr"/>
     </row>
     <row r="642">
       <c r="A642" s="1" t="inlineStr">
@@ -23089,11 +21649,7 @@
           <t>Montemor</t>
         </is>
       </c>
-      <c r="G643" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1171"}}</t>
-        </is>
-      </c>
+      <c r="G643" t="inlineStr"/>
     </row>
     <row r="644">
       <c r="A644" s="1" t="inlineStr">
@@ -23126,11 +21682,7 @@
           <t>Coimbra</t>
         </is>
       </c>
-      <c r="G644" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G644" t="inlineStr"/>
     </row>
     <row r="645">
       <c r="A645" s="1" t="inlineStr">
@@ -23163,11 +21715,7 @@
           <t>Guemara, diocese de Braga</t>
         </is>
       </c>
-      <c r="G645" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 17290802"}}</t>
-        </is>
-      </c>
+      <c r="G645" t="inlineStr"/>
     </row>
     <row r="646">
       <c r="A646" s="1" t="inlineStr">
@@ -23200,11 +21748,7 @@
           <t>Moreta, diocese de Coimbra</t>
         </is>
       </c>
-      <c r="G646" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G646" t="inlineStr"/>
     </row>
     <row r="647">
       <c r="A647" s="1" t="inlineStr">
@@ -23303,11 +21847,7 @@
           <t>Soure, diocese de Coimbra</t>
         </is>
       </c>
-      <c r="G649" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" s="1" t="inlineStr">
@@ -23340,11 +21880,7 @@
           <t>Lamego</t>
         </is>
       </c>
-      <c r="G650" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G650" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" s="1" t="inlineStr">
@@ -23509,11 +22045,7 @@
           <t>Évora</t>
         </is>
       </c>
-      <c r="G655" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G655" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" s="1" t="inlineStr">
@@ -23579,11 +22111,7 @@
           <t>Sousel, diocese de Évora</t>
         </is>
       </c>
-      <c r="G657" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q179948"}}</t>
-        </is>
-      </c>
+      <c r="G657" t="inlineStr"/>
     </row>
     <row r="658">
       <c r="A658" s="1" t="inlineStr">
@@ -23649,11 +22177,7 @@
           <t>Miranda do Douro, diocese de Bragança</t>
         </is>
       </c>
-      <c r="G659" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G659" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" s="1" t="inlineStr">
@@ -23686,11 +22210,7 @@
           <t>Arraiolos, diocese de Évora</t>
         </is>
       </c>
-      <c r="G660" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "aparece inscrito, mas depois o seu nome \u00e9 repetio em \u00c9vora, 16970925, ter\u00e1 sa\u00eddo no entretanto?"}}</t>
-        </is>
-      </c>
+      <c r="G660" t="inlineStr"/>
     </row>
     <row r="661">
       <c r="A661" s="1" t="inlineStr">
@@ -23723,11 +22243,7 @@
           <t>Marvão, diocese de Portalegre</t>
         </is>
       </c>
-      <c r="G661" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "o cat\u00e1logo de 1717 diz 17170509, a primeira data vem do cat\u00e1logo de 1734"}}</t>
-        </is>
-      </c>
+      <c r="G661" t="inlineStr"/>
     </row>
     <row r="662">
       <c r="A662" s="1" t="inlineStr">
@@ -23793,11 +22309,7 @@
           <t>Dijon</t>
         </is>
       </c>
-      <c r="G663" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q40898"}}</t>
-        </is>
-      </c>
+      <c r="G663" t="inlineStr"/>
     </row>
     <row r="664">
       <c r="A664" s="1" t="inlineStr">
@@ -23830,11 +22342,7 @@
           <t>Estremoz, diocese de Évora</t>
         </is>
       </c>
-      <c r="G664" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G664" t="inlineStr"/>
     </row>
     <row r="665">
       <c r="A665" s="1" t="inlineStr">
@@ -23933,11 +22441,7 @@
           <t>Trento</t>
         </is>
       </c>
-      <c r="G667" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G667" t="inlineStr"/>
     </row>
     <row r="668">
       <c r="A668" s="1" t="inlineStr">
@@ -23970,11 +22474,7 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G668" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412 MMHM:p.94 (ARSI Japsin 35 13)", "original": "?"}}</t>
-        </is>
-      </c>
+      <c r="G668" t="inlineStr"/>
     </row>
     <row r="669">
       <c r="A669" s="1" t="inlineStr">
@@ -24007,11 +22507,7 @@
           <t>S. Joaninho, diocese de Coimbra</t>
         </is>
       </c>
-      <c r="G669" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "para a China"}}</t>
-        </is>
-      </c>
+      <c r="G669" t="inlineStr"/>
     </row>
     <row r="670">
       <c r="A670" s="1" t="inlineStr">
@@ -24077,11 +22573,7 @@
           <t>Macau</t>
         </is>
       </c>
-      <c r="G671" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 1634"}}</t>
-        </is>
-      </c>
+      <c r="G671" t="inlineStr"/>
     </row>
     <row r="672">
       <c r="A672" s="1" t="inlineStr">
@@ -24114,11 +22606,7 @@
           <t>Aquitânia</t>
         </is>
       </c>
-      <c r="G672" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1479"}}</t>
-        </is>
-      </c>
+      <c r="G672" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" s="1" t="inlineStr">
@@ -24151,11 +22639,7 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G673" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G673" t="inlineStr"/>
     </row>
     <row r="674">
       <c r="A674" s="1" t="inlineStr">
@@ -24188,11 +22672,7 @@
           <t>Atalaia, diocese de Lisboa</t>
         </is>
       </c>
-      <c r="G674" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412 MMHM:p.203 (Matias d'Amaia), Schutte, Monumenta historica japoniae I.1234", "original": "?"}}</t>
-        </is>
-      </c>
+      <c r="G674" t="inlineStr"/>
     </row>
     <row r="675">
       <c r="A675" s="1" t="inlineStr">
@@ -24258,11 +22738,7 @@
           <t>Coimbra</t>
         </is>
       </c>
-      <c r="G676" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G676" t="inlineStr"/>
     </row>
     <row r="677">
       <c r="A677" s="1" t="inlineStr">
@@ -24295,11 +22771,7 @@
           <t>Macerata</t>
         </is>
       </c>
-      <c r="G677" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220", "original": "(Noviciado de Sant'Andrea al Quirinale)"}}</t>
-        </is>
-      </c>
+      <c r="G677" t="inlineStr"/>
     </row>
     <row r="678">
       <c r="A678" s="1" t="inlineStr">
@@ -24330,7 +22802,7 @@
       <c r="F678" t="inlineStr"/>
       <c r="G678" t="inlineStr">
         <is>
-          <t>depois de libertado da escravatura extra_info: {"date": {"comment": "[depois de 1615 que \u00e9 a data da persegui\u00e7\u00e3o ao padre Sebasti\u00e3o Fernandes- JRC]"}}</t>
+          <t>depois de libertado da escravatura</t>
         </is>
       </c>
     </row>
@@ -24365,11 +22837,7 @@
           <t>Pequim</t>
         </is>
       </c>
-      <c r="G679" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 17391100?"}, "value": {"comment": "? @wikidata:Q956"}}</t>
-        </is>
-      </c>
+      <c r="G679" t="inlineStr"/>
     </row>
     <row r="680">
       <c r="A680" s="1" t="inlineStr">
@@ -24402,11 +22870,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G680" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "segundo Ripa"}}</t>
-        </is>
-      </c>
+      <c r="G680" t="inlineStr"/>
     </row>
     <row r="681">
       <c r="A681" s="1" t="inlineStr">
@@ -24439,11 +22903,7 @@
           <t>Kouang-tong</t>
         </is>
       </c>
-      <c r="G681" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G681" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" s="1" t="inlineStr">
@@ -24476,11 +22936,7 @@
           <t>Vannes</t>
         </is>
       </c>
-      <c r="G682" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G682" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" s="1" t="inlineStr">
@@ -24513,11 +22969,7 @@
           <t>Celorico</t>
         </is>
       </c>
-      <c r="G683" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1171"}}</t>
-        </is>
-      </c>
+      <c r="G683" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" s="1" t="inlineStr">
@@ -24550,11 +23002,7 @@
           <t>Caravaca de la Cruz, diocese de Cartagena</t>
         </is>
       </c>
-      <c r="G684" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q46940"}}</t>
-        </is>
-      </c>
+      <c r="G684" t="inlineStr"/>
     </row>
     <row r="685">
       <c r="A685" s="1" t="inlineStr">
@@ -24587,11 +23035,7 @@
           <t>Viena</t>
         </is>
       </c>
-      <c r="G685" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
-        </is>
-      </c>
+      <c r="G685" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" s="1" t="inlineStr">
@@ -24624,11 +23068,7 @@
           <t>Lwów</t>
         </is>
       </c>
-      <c r="G686" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q31487"}}</t>
-        </is>
-      </c>
+      <c r="G686" t="inlineStr"/>
     </row>
     <row r="687">
       <c r="A687" s="1" t="inlineStr">
@@ -24661,11 +23101,7 @@
           <t>Munique</t>
         </is>
       </c>
-      <c r="G687" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q494299"}}</t>
-        </is>
-      </c>
+      <c r="G687" t="inlineStr"/>
     </row>
     <row r="688">
       <c r="A688" s="1" t="inlineStr">
@@ -24698,11 +23134,7 @@
           <t>Nanquim</t>
         </is>
       </c>
-      <c r="G688" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "\u00ablatinitate satis imbutus\u00bb"}, "value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G688" t="inlineStr"/>
     </row>
     <row r="689">
       <c r="A689" s="1" t="inlineStr">
@@ -24735,11 +23167,7 @@
           <t>Dijon (paróquia de St Jean)</t>
         </is>
       </c>
-      <c r="G689" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q40898"}}</t>
-        </is>
-      </c>
+      <c r="G689" t="inlineStr"/>
     </row>
     <row r="690">
       <c r="A690" s="1" t="inlineStr">
@@ -24805,11 +23233,7 @@
           <t>Douai</t>
         </is>
       </c>
-      <c r="G691" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45"}}</t>
-        </is>
-      </c>
+      <c r="G691" t="inlineStr"/>
     </row>
     <row r="692">
       <c r="A692" s="1" t="inlineStr">
@@ -24842,11 +23266,7 @@
           <t>Spinazzola, Bari</t>
         </is>
       </c>
-      <c r="G692" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G692" t="inlineStr"/>
     </row>
     <row r="693">
       <c r="A693" s="1" t="inlineStr">
@@ -24912,11 +23332,7 @@
           <t>Carapito ou Mangualde, diocese de Viseu</t>
         </is>
       </c>
-      <c r="G694" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G694" t="inlineStr"/>
     </row>
     <row r="695">
       <c r="A695" s="1" t="inlineStr">
@@ -24949,11 +23365,7 @@
           <t>Shiki, ilha de Amakusa</t>
         </is>
       </c>
-      <c r="G695" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "perto @wikidata:Q38234"}}</t>
-        </is>
-      </c>
+      <c r="G695" t="inlineStr"/>
     </row>
     <row r="696">
       <c r="A696" s="1" t="inlineStr">
@@ -24986,11 +23398,7 @@
           <t>Macau</t>
         </is>
       </c>
-      <c r="G696" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q14773"}}</t>
-        </is>
-      </c>
+      <c r="G696" t="inlineStr"/>
     </row>
     <row r="697">
       <c r="A697" s="1" t="inlineStr">
@@ -25089,11 +23497,7 @@
           <t>Pedroso, diocese do Porto</t>
         </is>
       </c>
-      <c r="G699" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 13, ou 17000311 ou 17050917"}, "value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G699" t="inlineStr"/>
     </row>
     <row r="700">
       <c r="A700" s="1" t="inlineStr">
@@ -25126,11 +23530,7 @@
           <t>Donauwörth</t>
         </is>
       </c>
-      <c r="G700" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q494299"}}</t>
-        </is>
-      </c>
+      <c r="G700" t="inlineStr"/>
     </row>
     <row r="701">
       <c r="A701" s="1" t="inlineStr">
@@ -25163,11 +23563,7 @@
           <t>Siena</t>
         </is>
       </c>
-      <c r="G701" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G701" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" s="1" t="inlineStr">
@@ -25233,11 +23629,7 @@
           <t>Caltagirone, Sicília</t>
         </is>
       </c>
-      <c r="G703" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "[Sic\u00edlia] @wikidata:Q13666"}}</t>
-        </is>
-      </c>
+      <c r="G703" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" s="1" t="inlineStr">
@@ -25303,11 +23695,7 @@
           <t>Valladolid</t>
         </is>
       </c>
-      <c r="G705" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q46940"}}</t>
-        </is>
-      </c>
+      <c r="G705" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" s="1" t="inlineStr">
@@ -25340,11 +23728,7 @@
           <t>Dijon</t>
         </is>
       </c>
-      <c r="G706" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q40898"}}</t>
-        </is>
-      </c>
+      <c r="G706" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" s="1" t="inlineStr">
@@ -25377,11 +23761,7 @@
           <t>Compiègne</t>
         </is>
       </c>
-      <c r="G707" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q6397"}}</t>
-        </is>
-      </c>
+      <c r="G707" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" s="1" t="inlineStr">
@@ -25414,11 +23794,7 @@
           <t>Douai</t>
         </is>
       </c>
-      <c r="G708" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "admitido"}, "value": {"comment": "admitido, entra em Tournai @wikidata:Q193826"}}</t>
-        </is>
-      </c>
+      <c r="G708" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" s="1" t="inlineStr">
@@ -25451,11 +23827,7 @@
           <t>Douai</t>
         </is>
       </c>
-      <c r="G709" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q173219"}}</t>
-        </is>
-      </c>
+      <c r="G709" t="inlineStr"/>
     </row>
     <row r="710">
       <c r="A710" s="1" t="inlineStr">
@@ -25521,11 +23893,7 @@
           <t>Macau</t>
         </is>
       </c>
-      <c r="G711" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G711" t="inlineStr"/>
     </row>
     <row r="712">
       <c r="A712" s="1" t="inlineStr">
@@ -25591,11 +23959,7 @@
           <t>Santarém</t>
         </is>
       </c>
-      <c r="G713" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G713" t="inlineStr"/>
     </row>
     <row r="714">
       <c r="A714" s="1" t="inlineStr">
@@ -25628,11 +23992,7 @@
           <t>Macau</t>
         </is>
       </c>
-      <c r="G714" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1171"}}</t>
-        </is>
-      </c>
+      <c r="G714" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" s="1" t="inlineStr">
@@ -25764,11 +24124,7 @@
           <t>Casto Val Sabbia, Brescia</t>
         </is>
       </c>
-      <c r="G718" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "j\u00e1 era padre"}, "value": {"comment": "@wikidata:Q13362"}}</t>
-        </is>
-      </c>
+      <c r="G718" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" s="1" t="inlineStr">
@@ -25966,11 +24322,7 @@
           <t>Macau</t>
         </is>
       </c>
-      <c r="G724" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q17"}}</t>
-        </is>
-      </c>
+      <c r="G724" t="inlineStr"/>
     </row>
     <row r="725">
       <c r="A725" s="1" t="inlineStr">
@@ -26003,11 +24355,7 @@
           <t>Macau</t>
         </is>
       </c>
-      <c r="G725" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "catequista"}}</t>
-        </is>
-      </c>
+      <c r="G725" t="inlineStr"/>
     </row>
     <row r="726">
       <c r="A726" s="1" t="inlineStr">
@@ -26040,11 +24388,7 @@
           <t>Bordeaux</t>
         </is>
       </c>
-      <c r="G726" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16730930"}}</t>
-        </is>
-      </c>
+      <c r="G726" t="inlineStr"/>
     </row>
     <row r="727">
       <c r="A727" s="1" t="inlineStr">
@@ -26077,11 +24421,7 @@
           <t>Kienchang, Kien-tch'ang fou, Kiangsi</t>
         </is>
       </c>
-      <c r="G727" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q4970"}}</t>
-        </is>
-      </c>
+      <c r="G727" t="inlineStr"/>
     </row>
     <row r="728">
       <c r="A728" s="1" t="inlineStr">
@@ -26114,11 +24454,7 @@
           <t>Vannes</t>
         </is>
       </c>
-      <c r="G728" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G728" t="inlineStr"/>
     </row>
     <row r="729">
       <c r="A729" s="1" t="inlineStr">
@@ -26184,11 +24520,7 @@
           <t>Chen-si</t>
         </is>
       </c>
-      <c r="G730" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 29 de junho"}, "value": {"comment": "@wikidata:Q14773"}}</t>
-        </is>
-      </c>
+      <c r="G730" t="inlineStr"/>
     </row>
     <row r="731">
       <c r="A731" s="1" t="inlineStr">
@@ -26254,11 +24586,7 @@
           <t>Basto, diocese de Braga</t>
         </is>
       </c>
-      <c r="G732" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G732" t="inlineStr"/>
     </row>
     <row r="733">
       <c r="A733" s="1" t="inlineStr">
@@ -26291,11 +24619,7 @@
           <t>Serpa, diocese de Évora</t>
         </is>
       </c>
-      <c r="G733" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q179948"}}</t>
-        </is>
-      </c>
+      <c r="G733" t="inlineStr"/>
     </row>
     <row r="734">
       <c r="A734" s="1" t="inlineStr">
@@ -26363,7 +24687,7 @@
       </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>saiu a primeira vez extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
+          <t>saiu a primeira vez</t>
         </is>
       </c>
     </row>
@@ -26398,11 +24722,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G736" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1171"}}</t>
-        </is>
-      </c>
+      <c r="G736" t="inlineStr"/>
     </row>
     <row r="737">
       <c r="A737" s="1" t="inlineStr">
@@ -26435,11 +24755,7 @@
           <t>Pombal</t>
         </is>
       </c>
-      <c r="G737" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "no mar, pela data de embarque seria em Lisboa?", "original": "in mari"}}</t>
-        </is>
-      </c>
+      <c r="G737" t="inlineStr"/>
     </row>
     <row r="738">
       <c r="A738" s="1" t="inlineStr">
@@ -26472,11 +24788,7 @@
           <t>Covilhã, diocese da Guarda</t>
         </is>
       </c>
-      <c r="G738" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 1581 segundo Wicki"}}</t>
-        </is>
-      </c>
+      <c r="G738" t="inlineStr"/>
     </row>
     <row r="739">
       <c r="A739" s="1" t="inlineStr">
@@ -26542,11 +24854,7 @@
           <t>Santo André</t>
         </is>
       </c>
-      <c r="G740" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G740" t="inlineStr"/>
     </row>
     <row r="741">
       <c r="A741" s="1" t="inlineStr">
@@ -26579,11 +24887,7 @@
           <t>Antequera, diocese de Málaga, Andaluzia</t>
         </is>
       </c>
-      <c r="G741" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "j\u00e1 era padre"}, "value": {"comment": "@wikidata:Q46940"}}</t>
-        </is>
-      </c>
+      <c r="G741" t="inlineStr"/>
     </row>
     <row r="742">
       <c r="A742" s="1" t="inlineStr">
@@ -26649,11 +24953,7 @@
           <t>Mourão, diocese de Évora</t>
         </is>
       </c>
-      <c r="G743" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "segundo Louren\u00e7o e Pinto 2023, p. 37"}}</t>
-        </is>
-      </c>
+      <c r="G743" t="inlineStr"/>
     </row>
     <row r="744">
       <c r="A744" s="1" t="inlineStr">
@@ -26686,11 +24986,7 @@
           <t>Coimbra</t>
         </is>
       </c>
-      <c r="G744" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G744" t="inlineStr"/>
     </row>
     <row r="745">
       <c r="A745" s="1" t="inlineStr">
@@ -26723,11 +25019,7 @@
           <t>Saragoça</t>
         </is>
       </c>
-      <c r="G745" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q46940", "original": "de Henares"}}</t>
-        </is>
-      </c>
+      <c r="G745" t="inlineStr"/>
     </row>
     <row r="746">
       <c r="A746" s="1" t="inlineStr">
@@ -26793,11 +25085,7 @@
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="G747" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G747" t="inlineStr"/>
     </row>
     <row r="748">
       <c r="A748" s="1" t="inlineStr">
@@ -26830,11 +25118,7 @@
           <t>Loures, diocese de Lisboa</t>
         </is>
       </c>
-      <c r="G748" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16320000"}}</t>
-        </is>
-      </c>
+      <c r="G748" t="inlineStr"/>
     </row>
     <row r="749">
       <c r="A749" s="1" t="inlineStr">
@@ -26929,11 +25213,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G751" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1171"}}</t>
-        </is>
-      </c>
+      <c r="G751" t="inlineStr"/>
     </row>
     <row r="752">
       <c r="A752" s="1" t="inlineStr">
@@ -27032,11 +25312,7 @@
           <t>Gorizia</t>
         </is>
       </c>
-      <c r="G754" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
-        </is>
-      </c>
+      <c r="G754" t="inlineStr"/>
     </row>
     <row r="755">
       <c r="A755" s="1" t="inlineStr">
@@ -27069,11 +25345,7 @@
           <t>Angoulême (paróquia de Notre-Dame de Beaulieu)</t>
         </is>
       </c>
-      <c r="G755" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1479"}}</t>
-        </is>
-      </c>
+      <c r="G755" t="inlineStr"/>
     </row>
     <row r="756">
       <c r="A756" s="1" t="inlineStr">
@@ -27106,11 +25378,7 @@
           <t>Menen, Bélgica</t>
         </is>
       </c>
-      <c r="G756" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q173219"}}</t>
-        </is>
-      </c>
+      <c r="G756" t="inlineStr"/>
     </row>
     <row r="757">
       <c r="A757" s="1" t="inlineStr">
@@ -27209,11 +25477,7 @@
           <t>Tourcoing</t>
         </is>
       </c>
-      <c r="G759" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q173219"}}</t>
-        </is>
-      </c>
+      <c r="G759" t="inlineStr"/>
     </row>
     <row r="760">
       <c r="A760" s="1" t="inlineStr">
@@ -27246,11 +25510,7 @@
           <t>Pequim</t>
         </is>
       </c>
-      <c r="G760" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "depois dos seus estudos"}, "value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G760" t="inlineStr"/>
     </row>
     <row r="761">
       <c r="A761" s="1" t="inlineStr">
@@ -27316,11 +25576,7 @@
           <t>Angers</t>
         </is>
       </c>
-      <c r="G762" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G762" t="inlineStr"/>
     </row>
     <row r="763">
       <c r="A763" s="1" t="inlineStr">
@@ -27353,11 +25609,7 @@
           <t>Diocese de Avignon</t>
         </is>
       </c>
-      <c r="G763" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q456"}}</t>
-        </is>
-      </c>
+      <c r="G763" t="inlineStr"/>
     </row>
     <row r="764">
       <c r="A764" s="1" t="inlineStr">
@@ -27423,11 +25675,7 @@
           <t>Rouen</t>
         </is>
       </c>
-      <c r="G765" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G765" t="inlineStr"/>
     </row>
     <row r="766">
       <c r="A766" s="1" t="inlineStr">
@@ -27526,11 +25774,7 @@
           <t>Diocese de Mans</t>
         </is>
       </c>
-      <c r="G768" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G768" t="inlineStr"/>
     </row>
     <row r="769">
       <c r="A769" s="1" t="inlineStr">
@@ -27629,11 +25873,7 @@
           <t>Diocese de Albi</t>
         </is>
       </c>
-      <c r="G771" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "Toulouse? @wikidata:Q7880"}}</t>
-        </is>
-      </c>
+      <c r="G771" t="inlineStr"/>
     </row>
     <row r="772">
       <c r="A772" s="1" t="inlineStr">
@@ -27666,11 +25906,7 @@
           <t>Embrun</t>
         </is>
       </c>
-      <c r="G772" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q6397"}}</t>
-        </is>
-      </c>
+      <c r="G772" t="inlineStr"/>
     </row>
     <row r="773">
       <c r="A773" s="1" t="inlineStr">
@@ -27703,11 +25939,7 @@
           <t>Shaohing (Chao-hing fou, Tchö-kiang)</t>
         </is>
       </c>
-      <c r="G773" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q956"}}</t>
-        </is>
-      </c>
+      <c r="G773" t="inlineStr"/>
     </row>
     <row r="774">
       <c r="A774" s="1" t="inlineStr">
@@ -27740,11 +25972,7 @@
           <t>Champagne, Turny (Yonne)</t>
         </is>
       </c>
-      <c r="G774" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 17440730"}, "value": {"comment": "@wikidata:Q40898"}}</t>
-        </is>
-      </c>
+      <c r="G774" t="inlineStr"/>
     </row>
     <row r="775">
       <c r="A775" s="1" t="inlineStr">
@@ -27777,11 +26005,7 @@
           <t>Limoges</t>
         </is>
       </c>
-      <c r="G775" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1479"}}</t>
-        </is>
-      </c>
+      <c r="G775" t="inlineStr"/>
     </row>
     <row r="776">
       <c r="A776" s="1" t="inlineStr">
@@ -27814,11 +26038,7 @@
           <t>Limoges</t>
         </is>
       </c>
-      <c r="G776" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1479"}}</t>
-        </is>
-      </c>
+      <c r="G776" t="inlineStr"/>
     </row>
     <row r="777">
       <c r="A777" s="1" t="inlineStr">
@@ -27884,11 +26104,7 @@
           <t>Louviers, diocese de Evreux</t>
         </is>
       </c>
-      <c r="G778" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G778" t="inlineStr"/>
     </row>
     <row r="779">
       <c r="A779" s="1" t="inlineStr">
@@ -27987,11 +26203,7 @@
           <t>Lyon</t>
         </is>
       </c>
-      <c r="G781" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q456"}}</t>
-        </is>
-      </c>
+      <c r="G781" t="inlineStr"/>
     </row>
     <row r="782">
       <c r="A782" s="1" t="inlineStr">
@@ -28057,11 +26269,7 @@
           <t>Douai</t>
         </is>
       </c>
-      <c r="G783" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G783" t="inlineStr"/>
     </row>
     <row r="784">
       <c r="A784" s="1" t="inlineStr">
@@ -28094,11 +26302,7 @@
           <t>Diocese de Rodez</t>
         </is>
       </c>
-      <c r="G784" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "em 1758 n\u00e3o era ainda Padre"}}</t>
-        </is>
-      </c>
+      <c r="G784" t="inlineStr"/>
     </row>
     <row r="785">
       <c r="A785" s="1" t="inlineStr">
@@ -28131,11 +26335,7 @@
           <t>Pont-à-Mousson</t>
         </is>
       </c>
-      <c r="G785" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q40898"}}</t>
-        </is>
-      </c>
+      <c r="G785" t="inlineStr"/>
     </row>
     <row r="786">
       <c r="A786" s="1" t="inlineStr">
@@ -28168,11 +26368,7 @@
           <t>Gand</t>
         </is>
       </c>
-      <c r="G786" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q162022", "original": "Malines"}}</t>
-        </is>
-      </c>
+      <c r="G786" t="inlineStr"/>
     </row>
     <row r="787">
       <c r="A787" s="1" t="inlineStr">
@@ -28238,11 +26434,7 @@
           <t>Génova</t>
         </is>
       </c>
-      <c r="G788" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G788" t="inlineStr"/>
     </row>
     <row r="789">
       <c r="A789" s="1" t="inlineStr">
@@ -28440,11 +26632,7 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G794" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G794" t="inlineStr"/>
     </row>
     <row r="795">
       <c r="A795" s="1" t="inlineStr">
@@ -28477,11 +26665,7 @@
           <t>Normandia</t>
         </is>
       </c>
-      <c r="G795" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "? @wikidata:Q14773"}}</t>
-        </is>
-      </c>
+      <c r="G795" t="inlineStr"/>
     </row>
     <row r="796">
       <c r="A796" s="1" t="inlineStr">
@@ -28514,11 +26698,7 @@
           <t>Reiningue</t>
         </is>
       </c>
-      <c r="G796" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q494299"}}</t>
-        </is>
-      </c>
+      <c r="G796" t="inlineStr"/>
     </row>
     <row r="797">
       <c r="A797" s="1" t="inlineStr">
@@ -28551,11 +26731,7 @@
           <t>Mora, diocese de Évora</t>
         </is>
       </c>
-      <c r="G797" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 15721228"}}</t>
-        </is>
-      </c>
+      <c r="G797" t="inlineStr"/>
     </row>
     <row r="798">
       <c r="A798" s="1" t="inlineStr">
@@ -28588,11 +26764,7 @@
           <t>Coruche, diocese de Évora</t>
         </is>
       </c>
-      <c r="G798" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q179948"}}</t>
-        </is>
-      </c>
+      <c r="G798" t="inlineStr"/>
     </row>
     <row r="799">
       <c r="A799" s="1" t="inlineStr">
@@ -28625,11 +26797,7 @@
           <t>Lecce, Itália</t>
         </is>
       </c>
-      <c r="G799" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q2634"}}</t>
-        </is>
-      </c>
+      <c r="G799" t="inlineStr"/>
     </row>
     <row r="800">
       <c r="A800" s="1" t="inlineStr">
@@ -28695,11 +26863,7 @@
           <t>Semide, diocese de Coimbra</t>
         </is>
       </c>
-      <c r="G801" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597", "original": "Lisboa, Arroios"}}</t>
-        </is>
-      </c>
+      <c r="G801" t="inlineStr"/>
     </row>
     <row r="802">
       <c r="A802" s="1" t="inlineStr">
@@ -28732,11 +26896,7 @@
           <t>Macau</t>
         </is>
       </c>
-      <c r="G802" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "cerca de"}}</t>
-        </is>
-      </c>
+      <c r="G802" t="inlineStr"/>
     </row>
     <row r="803">
       <c r="A803" s="1" t="inlineStr">
@@ -28769,11 +26929,7 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G803" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412 MMHM:p.205 (Sebastian da Maia, da Maya, d'Amaya)", "original": "?"}}</t>
-        </is>
-      </c>
+      <c r="G803" t="inlineStr"/>
     </row>
     <row r="804">
       <c r="A804" s="1" t="inlineStr">
@@ -28806,11 +26962,7 @@
           <t>Lagéas</t>
         </is>
       </c>
-      <c r="G804" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1171"}}</t>
-        </is>
-      </c>
+      <c r="G804" t="inlineStr"/>
     </row>
     <row r="805">
       <c r="A805" s="1" t="inlineStr">
@@ -28843,11 +26995,7 @@
           <t>Besteiros, diocese de Viseu</t>
         </is>
       </c>
-      <c r="G805" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G805" t="inlineStr"/>
     </row>
     <row r="806">
       <c r="A806" s="1" t="inlineStr">
@@ -28880,11 +27028,7 @@
           <t>Castro Daire, diocese de Lamego</t>
         </is>
       </c>
-      <c r="G806" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "([Sch\u00fctte, 1975, p. 1321] Sebasti\u00e3o Vieira, nasc Castro de Aire, Lamego, E. Coimbra 3-2-1591", "original": "?"}}</t>
-        </is>
-      </c>
+      <c r="G806" t="inlineStr"/>
     </row>
     <row r="807">
       <c r="A807" s="1" t="inlineStr">
@@ -28917,11 +27061,7 @@
           <t>Sunwui (Sin-houei)</t>
         </is>
       </c>
-      <c r="G807" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "fim do m\u00eas"}, "value": {"comment": "@wikidata: Q1346617", "original": "Chao-tcheou fou"}}</t>
-        </is>
-      </c>
+      <c r="G807" t="inlineStr"/>
     </row>
     <row r="808">
       <c r="A808" s="1" t="inlineStr">
@@ -28987,11 +27127,7 @@
           <t>Coimbra</t>
         </is>
       </c>
-      <c r="G809" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412 Dehergne n\u00e3o especifica local, Brockey estudos Filosofia e Teologia em Coimbra", "original": "?"}}</t>
-        </is>
-      </c>
+      <c r="G809" t="inlineStr"/>
     </row>
     <row r="810">
       <c r="A810" s="1" t="inlineStr">
@@ -29024,11 +27160,7 @@
           <t>Borba, diocese de Évora</t>
         </is>
       </c>
-      <c r="G810" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q179948"}}</t>
-        </is>
-      </c>
+      <c r="G810" t="inlineStr"/>
     </row>
     <row r="811">
       <c r="A811" s="1" t="inlineStr">
@@ -29094,11 +27226,7 @@
           <t>Vila Pouca do Campo, diocese de Coimbra</t>
         </is>
       </c>
-      <c r="G812" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1171"}}</t>
-        </is>
-      </c>
+      <c r="G812" t="inlineStr"/>
     </row>
     <row r="813">
       <c r="A813" s="1" t="inlineStr">
@@ -29230,11 +27358,7 @@
           <t>Wenns, Áustria</t>
         </is>
       </c>
-      <c r="G816" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q494299"}}</t>
-        </is>
-      </c>
+      <c r="G816" t="inlineStr"/>
     </row>
     <row r="817">
       <c r="A817" s="1" t="inlineStr">
@@ -29267,11 +27391,7 @@
           <t>Changshu, Tch'ang-chou, Kiangnan</t>
         </is>
       </c>
-      <c r="G817" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q14773"}}</t>
-        </is>
-      </c>
+      <c r="G817" t="inlineStr"/>
     </row>
     <row r="818">
       <c r="A818" s="1" t="inlineStr">
@@ -29304,11 +27424,7 @@
           <t>Orvieto</t>
         </is>
       </c>
-      <c r="G818" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220", "original": "(Noviciado de Sant'Andrea al Quirinale)"}}</t>
-        </is>
-      </c>
+      <c r="G818" t="inlineStr"/>
     </row>
     <row r="819">
       <c r="A819" s="1" t="inlineStr">
@@ -29374,11 +27490,7 @@
           <t>Hangchow, Chekiang</t>
         </is>
       </c>
-      <c r="G820" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 17490202"}}</t>
-        </is>
-      </c>
+      <c r="G820" t="inlineStr"/>
     </row>
     <row r="821">
       <c r="A821" s="1" t="inlineStr">
@@ -29473,11 +27585,7 @@
           <t>Liège</t>
         </is>
       </c>
-      <c r="G823" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q220"}}</t>
-        </is>
-      </c>
+      <c r="G823" t="inlineStr"/>
     </row>
     <row r="824">
       <c r="A824" s="1" t="inlineStr">
@@ -29510,11 +27618,7 @@
           <t>Flandres</t>
         </is>
       </c>
-      <c r="G824" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
-        </is>
-      </c>
+      <c r="G824" t="inlineStr"/>
     </row>
     <row r="825">
       <c r="A825" s="1" t="inlineStr">
@@ -29547,11 +27651,7 @@
           <t>Hangchow, Chekiang</t>
         </is>
       </c>
-      <c r="G825" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q14773"}}</t>
-        </is>
-      </c>
+      <c r="G825" t="inlineStr"/>
     </row>
     <row r="826">
       <c r="A826" s="1" t="inlineStr">
@@ -29584,11 +27684,7 @@
           <t>Kiangsi</t>
         </is>
       </c>
-      <c r="G826" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 30 ou 29"}}</t>
-        </is>
-      </c>
+      <c r="G826" t="inlineStr"/>
     </row>
     <row r="827">
       <c r="A827" s="1" t="inlineStr">
@@ -29621,11 +27717,7 @@
           <t>Pequim</t>
         </is>
       </c>
-      <c r="G827" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G827" t="inlineStr"/>
     </row>
     <row r="828">
       <c r="A828" s="1" t="inlineStr">
@@ -29658,11 +27750,7 @@
           <t>Pequim</t>
         </is>
       </c>
-      <c r="G828" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 1 de novembro"}}</t>
-        </is>
-      </c>
+      <c r="G828" t="inlineStr"/>
     </row>
     <row r="829">
       <c r="A829" s="1" t="inlineStr">
@@ -29695,11 +27783,7 @@
           <t>Bruxelas</t>
         </is>
       </c>
-      <c r="G829" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q162022", "original": "Malines"}}</t>
-        </is>
-      </c>
+      <c r="G829" t="inlineStr"/>
     </row>
     <row r="830">
       <c r="A830" s="1" t="inlineStr">
@@ -29732,11 +27816,7 @@
           <t>Santarém</t>
         </is>
       </c>
-      <c r="G830" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G830" t="inlineStr"/>
     </row>
     <row r="831">
       <c r="A831" s="1" t="inlineStr">
@@ -29769,11 +27849,7 @@
           <t>Diocese de Auxerre</t>
         </is>
       </c>
-      <c r="G831" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G831" t="inlineStr"/>
     </row>
     <row r="832">
       <c r="A832" s="1" t="inlineStr">
@@ -29806,11 +27882,7 @@
           <t>Sousa, diocese de Coimbra</t>
         </is>
       </c>
-      <c r="G832" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 17480000"}}</t>
-        </is>
-      </c>
+      <c r="G832" t="inlineStr"/>
     </row>
     <row r="833">
       <c r="A833" s="1" t="inlineStr">
@@ -29843,11 +27915,7 @@
           <t>S. Martinho do Vale, diocese de Braga</t>
         </is>
       </c>
-      <c r="G833" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q45412"}}</t>
-        </is>
-      </c>
+      <c r="G833" t="inlineStr"/>
     </row>
     <row r="834">
       <c r="A834" s="1" t="inlineStr">
@@ -29880,11 +27948,7 @@
           <t>Viana do Alentejo, diocese de Évora</t>
         </is>
       </c>
-      <c r="G834" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 1646"}, "value": {"comment": "@wikidata:Q179948"}}</t>
-        </is>
-      </c>
+      <c r="G834" t="inlineStr"/>
     </row>
     <row r="835">
       <c r="A835" s="1" t="inlineStr">
@@ -29950,11 +28014,7 @@
           <t>Angers</t>
         </is>
       </c>
-      <c r="G836" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q90"}}</t>
-        </is>
-      </c>
+      <c r="G836" t="inlineStr"/>
     </row>
     <row r="837">
       <c r="A837" s="1" t="inlineStr">
@@ -29987,11 +28047,7 @@
           <t>Modena</t>
         </is>
       </c>
-      <c r="G837" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "[Assume-se Novellara, nascido a 40km] @wikidata:Q111218", "original": "Novellario"}}</t>
-        </is>
-      </c>
+      <c r="G837" t="inlineStr"/>
     </row>
     <row r="838">
       <c r="A838" s="1" t="inlineStr">
@@ -30024,11 +28080,7 @@
           <t>Frioul (no palácio dos condes d'Attimis)</t>
         </is>
       </c>
-      <c r="G838" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "en fait 17251129"}, "value": {"comment": "@wikidata:Q1891"}}</t>
-        </is>
-      </c>
+      <c r="G838" t="inlineStr"/>
     </row>
     <row r="839">
       <c r="A839" s="1" t="inlineStr">
@@ -30061,11 +28113,7 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G839" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "MMHM:p.38, 17 anos", "original": "?"}}</t>
-        </is>
-      </c>
+      <c r="G839" t="inlineStr"/>
     </row>
     <row r="840">
       <c r="A840" s="1" t="inlineStr">
@@ -30197,11 +28245,7 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G843" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q14773"}}</t>
-        </is>
-      </c>
+      <c r="G843" t="inlineStr"/>
     </row>
     <row r="844">
       <c r="A844" s="1" t="inlineStr">
@@ -30234,11 +28278,7 @@
           <t>Vamias, diocese de Viseu</t>
         </is>
       </c>
-      <c r="G844" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "destinado \u00e0 China"}, "value": {"comment": "@wikidata:Q597", "original": "Lisboa, Arroios"}}</t>
-        </is>
-      </c>
+      <c r="G844" t="inlineStr"/>
     </row>
     <row r="845">
       <c r="A845" s="1" t="inlineStr">
@@ -30271,11 +28311,7 @@
           <t>Coreia</t>
         </is>
       </c>
-      <c r="G845" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "mesmo antes do seu mart\u00edrio"}, "value": {"comment": "@wikidata:Q17"}}</t>
-        </is>
-      </c>
+      <c r="G845" t="inlineStr"/>
     </row>
     <row r="846">
       <c r="A846" s="1" t="inlineStr">
@@ -30407,11 +28443,7 @@
           <t>Praga</t>
         </is>
       </c>
-      <c r="G849" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "[Rep\u00fablica Checa] @wikidata:Q14960"}}</t>
-        </is>
-      </c>
+      <c r="G849" t="inlineStr"/>
     </row>
     <row r="850">
       <c r="A850" s="1" t="inlineStr">
@@ -30444,11 +28476,7 @@
           <t>Kadaň, Boémia</t>
         </is>
       </c>
-      <c r="G850" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "[Rep\u00fablica Checa] @wikidata:Q14960"}}</t>
-        </is>
-      </c>
+      <c r="G850" t="inlineStr"/>
     </row>
     <row r="851">
       <c r="A851" s="1" t="inlineStr">
@@ -30481,11 +28509,7 @@
           <t>Coimbra</t>
         </is>
       </c>
-      <c r="G851" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 17361104"}}</t>
-        </is>
-      </c>
+      <c r="G851" t="inlineStr"/>
     </row>
     <row r="852">
       <c r="A852" s="1" t="inlineStr">
